--- a/province_melt.xlsx
+++ b/province_melt.xlsx
@@ -488,7 +488,7 @@
         <v>2010</v>
       </c>
       <c r="G2" t="n">
-        <v>8.741854827374732</v>
+        <v>8.214485311123587</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>2010</v>
       </c>
       <c r="G3" t="n">
-        <v>4.075620335371686</v>
+        <v>4.364283725930794</v>
       </c>
     </row>
     <row r="4">
@@ -550,7 +550,7 @@
         <v>2010</v>
       </c>
       <c r="G4" t="n">
-        <v>14.20237395839058</v>
+        <v>15.90338472910628</v>
       </c>
     </row>
     <row r="5">
@@ -581,7 +581,7 @@
         <v>2010</v>
       </c>
       <c r="G5" t="n">
-        <v>29.77905122869172</v>
+        <v>29.03356706241316</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         <v>2010</v>
       </c>
       <c r="G6" t="n">
-        <v>16.22314052881885</v>
+        <v>16.22734262108815</v>
       </c>
     </row>
     <row r="7">
@@ -643,7 +643,7 @@
         <v>2010</v>
       </c>
       <c r="G7" t="n">
-        <v>9.389083143789057</v>
+        <v>9.613822620513341</v>
       </c>
     </row>
     <row r="8">
@@ -674,7 +674,7 @@
         <v>2010</v>
       </c>
       <c r="G8" t="n">
-        <v>14.67946858873999</v>
+        <v>13.09349749673657</v>
       </c>
     </row>
     <row r="9">
@@ -705,7 +705,7 @@
         <v>2010</v>
       </c>
       <c r="G9" t="n">
-        <v>15.505192897314</v>
+        <v>17.44174637883639</v>
       </c>
     </row>
     <row r="10">
@@ -736,7 +736,7 @@
         <v>2010</v>
       </c>
       <c r="G10" t="n">
-        <v>13.70331679529929</v>
+        <v>13.63444513450439</v>
       </c>
     </row>
     <row r="11">
@@ -767,7 +767,7 @@
         <v>2010</v>
       </c>
       <c r="G11" t="n">
-        <v>15.52702666655578</v>
+        <v>15.46224642402208</v>
       </c>
     </row>
     <row r="12">
@@ -798,7 +798,7 @@
         <v>2010</v>
       </c>
       <c r="G12" t="n">
-        <v>10.67130430194965</v>
+        <v>8.813816974730619</v>
       </c>
     </row>
     <row r="13">
@@ -829,7 +829,7 @@
         <v>2010</v>
       </c>
       <c r="G13" t="n">
-        <v>27.33131650109654</v>
+        <v>25.65842729733427</v>
       </c>
     </row>
     <row r="14">
@@ -860,7 +860,7 @@
         <v>2010</v>
       </c>
       <c r="G14" t="n">
-        <v>20.78879886529805</v>
+        <v>20.71425591116886</v>
       </c>
     </row>
     <row r="15">
@@ -891,7 +891,7 @@
         <v>2010</v>
       </c>
       <c r="G15" t="n">
-        <v>18.84378101813952</v>
+        <v>18.47254313586624</v>
       </c>
     </row>
     <row r="16">
@@ -922,7 +922,7 @@
         <v>2010</v>
       </c>
       <c r="G16" t="n">
-        <v>18.07014096378136</v>
+        <v>17.56662424557803</v>
       </c>
     </row>
     <row r="17">
@@ -953,7 +953,7 @@
         <v>2010</v>
       </c>
       <c r="G17" t="n">
-        <v>16.32287555149923</v>
+        <v>16.22986864441133</v>
       </c>
     </row>
     <row r="18">
@@ -984,7 +984,7 @@
         <v>2010</v>
       </c>
       <c r="G18" t="n">
-        <v>16.24235569035427</v>
+        <v>17.11901084821293</v>
       </c>
     </row>
     <row r="19">
@@ -1015,7 +1015,7 @@
         <v>2010</v>
       </c>
       <c r="G19" t="n">
-        <v>16.31327743108502</v>
+        <v>15.54459011616227</v>
       </c>
     </row>
     <row r="20">
@@ -1046,7 +1046,7 @@
         <v>2010</v>
       </c>
       <c r="G20" t="n">
-        <v>10.33437930231332</v>
+        <v>10.55001218929782</v>
       </c>
     </row>
     <row r="21">
@@ -1077,7 +1077,7 @@
         <v>2010</v>
       </c>
       <c r="G21" t="n">
-        <v>9.108291057610735</v>
+        <v>8.374309068643342</v>
       </c>
     </row>
     <row r="22">
@@ -1108,7 +1108,7 @@
         <v>2010</v>
       </c>
       <c r="G22" t="n">
-        <v>10.30336700807837</v>
+        <v>12.9443305528397</v>
       </c>
     </row>
     <row r="23">
@@ -1139,7 +1139,7 @@
         <v>2010</v>
       </c>
       <c r="G23" t="n">
-        <v>15.14766106091487</v>
+        <v>16.24323511687749</v>
       </c>
     </row>
     <row r="24">
@@ -1170,7 +1170,7 @@
         <v>2010</v>
       </c>
       <c r="G24" t="n">
-        <v>10.69628244026855</v>
+        <v>11.46483687537244</v>
       </c>
     </row>
     <row r="25">
@@ -1201,7 +1201,7 @@
         <v>2010</v>
       </c>
       <c r="G25" t="n">
-        <v>12.11729246861051</v>
+        <v>11.70643855500209</v>
       </c>
     </row>
     <row r="26">
@@ -1232,7 +1232,7 @@
         <v>2010</v>
       </c>
       <c r="G26" t="n">
-        <v>8.712398554166207</v>
+        <v>10.56438346574383</v>
       </c>
     </row>
     <row r="27">
@@ -1263,7 +1263,7 @@
         <v>2010</v>
       </c>
       <c r="G27" t="n">
-        <v>8.518368755441813</v>
+        <v>9.891349133533591</v>
       </c>
     </row>
     <row r="28">
@@ -1294,7 +1294,7 @@
         <v>2010</v>
       </c>
       <c r="G28" t="n">
-        <v>17.29187522419878</v>
+        <v>17.04599717054467</v>
       </c>
     </row>
     <row r="29">
@@ -1325,7 +1325,7 @@
         <v>2010</v>
       </c>
       <c r="G29" t="n">
-        <v>12.49597417629429</v>
+        <v>10.76005762571984</v>
       </c>
     </row>
     <row r="30">
@@ -1356,7 +1356,7 @@
         <v>2010</v>
       </c>
       <c r="G30" t="n">
-        <v>11.96065058523524</v>
+        <v>9.630185121083256</v>
       </c>
     </row>
     <row r="31">
@@ -1387,7 +1387,7 @@
         <v>2010</v>
       </c>
       <c r="G31" t="n">
-        <v>6.254928818780242</v>
+        <v>7.518799174276801</v>
       </c>
     </row>
     <row r="32">
@@ -1418,7 +1418,7 @@
         <v>2010</v>
       </c>
       <c r="G32" t="n">
-        <v>8.248735731901945</v>
+        <v>8.475964984255304</v>
       </c>
     </row>
     <row r="33">
@@ -1449,7 +1449,7 @@
         <v>2011</v>
       </c>
       <c r="G33" t="n">
-        <v>13.66476582889729</v>
+        <v>14.28583491656973</v>
       </c>
     </row>
     <row r="34">
@@ -1480,7 +1480,7 @@
         <v>2011</v>
       </c>
       <c r="G34" t="n">
-        <v>7.376244220065424</v>
+        <v>7.788241927779066</v>
       </c>
     </row>
     <row r="35">
@@ -1511,7 +1511,7 @@
         <v>2011</v>
       </c>
       <c r="G35" t="n">
-        <v>19.28859690652793</v>
+        <v>20.81830481364848</v>
       </c>
     </row>
     <row r="36">
@@ -1542,7 +1542,7 @@
         <v>2011</v>
       </c>
       <c r="G36" t="n">
-        <v>29.38265492428597</v>
+        <v>30.05001394123334</v>
       </c>
     </row>
     <row r="37">
@@ -1573,7 +1573,7 @@
         <v>2011</v>
       </c>
       <c r="G37" t="n">
-        <v>9.669251466317764</v>
+        <v>10.36616982127496</v>
       </c>
     </row>
     <row r="38">
@@ -1604,7 +1604,7 @@
         <v>2011</v>
       </c>
       <c r="G38" t="n">
-        <v>11.53369307927566</v>
+        <v>12.08084923202405</v>
       </c>
     </row>
     <row r="39">
@@ -1635,7 +1635,7 @@
         <v>2011</v>
       </c>
       <c r="G39" t="n">
-        <v>13.23687891821735</v>
+        <v>13.66433782264116</v>
       </c>
     </row>
     <row r="40">
@@ -1666,7 +1666,7 @@
         <v>2011</v>
       </c>
       <c r="G40" t="n">
-        <v>10.2984692931711</v>
+        <v>11.08481589662395</v>
       </c>
     </row>
     <row r="41">
@@ -1697,7 +1697,7 @@
         <v>2011</v>
       </c>
       <c r="G41" t="n">
-        <v>8.19618257260152</v>
+        <v>7.268500250712052</v>
       </c>
     </row>
     <row r="42">
@@ -1728,7 +1728,7 @@
         <v>2011</v>
       </c>
       <c r="G42" t="n">
-        <v>14.0613558749947</v>
+        <v>14.59668941484651</v>
       </c>
     </row>
     <row r="43">
@@ -1759,7 +1759,7 @@
         <v>2011</v>
       </c>
       <c r="G43" t="n">
-        <v>8.378013851598668</v>
+        <v>7.962109622638234</v>
       </c>
     </row>
     <row r="44">
@@ -1790,7 +1790,7 @@
         <v>2011</v>
       </c>
       <c r="G44" t="n">
-        <v>16.4154402250738</v>
+        <v>16.23217879671781</v>
       </c>
     </row>
     <row r="45">
@@ -1821,7 +1821,7 @@
         <v>2011</v>
       </c>
       <c r="G45" t="n">
-        <v>10.64367716804615</v>
+        <v>10.73406534110862</v>
       </c>
     </row>
     <row r="46">
@@ -1852,7 +1852,7 @@
         <v>2011</v>
       </c>
       <c r="G46" t="n">
-        <v>21.18229502624111</v>
+        <v>21.26791075742956</v>
       </c>
     </row>
     <row r="47">
@@ -1883,7 +1883,7 @@
         <v>2011</v>
       </c>
       <c r="G47" t="n">
-        <v>12.71745348505196</v>
+        <v>13.16368779888057</v>
       </c>
     </row>
     <row r="48">
@@ -1914,7 +1914,7 @@
         <v>2011</v>
       </c>
       <c r="G48" t="n">
-        <v>5.95398265251854</v>
+        <v>5.359767822242444</v>
       </c>
     </row>
     <row r="49">
@@ -1945,7 +1945,7 @@
         <v>2011</v>
       </c>
       <c r="G49" t="n">
-        <v>17.08440578893437</v>
+        <v>17.20833773295264</v>
       </c>
     </row>
     <row r="50">
@@ -1976,7 +1976,7 @@
         <v>2011</v>
       </c>
       <c r="G50" t="n">
-        <v>7.500684432391997</v>
+        <v>7.649666659374938</v>
       </c>
     </row>
     <row r="51">
@@ -2007,7 +2007,7 @@
         <v>2011</v>
       </c>
       <c r="G51" t="n">
-        <v>11.90910241753803</v>
+        <v>12.03645290495467</v>
       </c>
     </row>
     <row r="52">
@@ -2038,7 +2038,7 @@
         <v>2011</v>
       </c>
       <c r="G52" t="n">
-        <v>7.259457571211514</v>
+        <v>7.602109683055687</v>
       </c>
     </row>
     <row r="53">
@@ -2069,7 +2069,7 @@
         <v>2011</v>
       </c>
       <c r="G53" t="n">
-        <v>5.93723488552844</v>
+        <v>7.004128390020424</v>
       </c>
     </row>
     <row r="54">
@@ -2100,7 +2100,7 @@
         <v>2011</v>
       </c>
       <c r="G54" t="n">
-        <v>12.6524699098615</v>
+        <v>14.0027345374162</v>
       </c>
     </row>
     <row r="55">
@@ -2131,7 +2131,7 @@
         <v>2011</v>
       </c>
       <c r="G55" t="n">
-        <v>28.35931148318637</v>
+        <v>27.78231060965273</v>
       </c>
     </row>
     <row r="56">
@@ -2162,7 +2162,7 @@
         <v>2011</v>
       </c>
       <c r="G56" t="n">
-        <v>16.38405181578103</v>
+        <v>17.43621949399602</v>
       </c>
     </row>
     <row r="57">
@@ -2193,7 +2193,7 @@
         <v>2011</v>
       </c>
       <c r="G57" t="n">
-        <v>8.438099244344913</v>
+        <v>9.122560584739507</v>
       </c>
     </row>
     <row r="58">
@@ -2224,7 +2224,7 @@
         <v>2011</v>
       </c>
       <c r="G58" t="n">
-        <v>9.657687168510719</v>
+        <v>9.449480791377487</v>
       </c>
     </row>
     <row r="59">
@@ -2255,7 +2255,7 @@
         <v>2011</v>
       </c>
       <c r="G59" t="n">
-        <v>6.80784566997557</v>
+        <v>8.342913795266147</v>
       </c>
     </row>
     <row r="60">
@@ -2286,7 +2286,7 @@
         <v>2011</v>
       </c>
       <c r="G60" t="n">
-        <v>2.104956757651023</v>
+        <v>1.545906156089259</v>
       </c>
     </row>
     <row r="61">
@@ -2317,7 +2317,7 @@
         <v>2011</v>
       </c>
       <c r="G61" t="n">
-        <v>8.354662541418504</v>
+        <v>7.288937680649638</v>
       </c>
     </row>
     <row r="62">
@@ -2348,7 +2348,7 @@
         <v>2011</v>
       </c>
       <c r="G62" t="n">
-        <v>7.513240635863696</v>
+        <v>8.595269865937547</v>
       </c>
     </row>
     <row r="63">
@@ -2379,7 +2379,7 @@
         <v>2011</v>
       </c>
       <c r="G63" t="n">
-        <v>3.849957669941248</v>
+        <v>3.962112806688133</v>
       </c>
     </row>
     <row r="64">
@@ -2410,7 +2410,7 @@
         <v>2012</v>
       </c>
       <c r="G64" t="n">
-        <v>8.047598693608021</v>
+        <v>8.134769148731134</v>
       </c>
     </row>
     <row r="65">
@@ -2441,7 +2441,7 @@
         <v>2012</v>
       </c>
       <c r="G65" t="n">
-        <v>7.209466552294621</v>
+        <v>7.044366447751012</v>
       </c>
     </row>
     <row r="66">
@@ -2472,7 +2472,7 @@
         <v>2012</v>
       </c>
       <c r="G66" t="n">
-        <v>12.9010866794706</v>
+        <v>11.91140597474877</v>
       </c>
     </row>
     <row r="67">
@@ -2503,7 +2503,7 @@
         <v>2012</v>
       </c>
       <c r="G67" t="n">
-        <v>30.37749895176984</v>
+        <v>29.00834799207733</v>
       </c>
     </row>
     <row r="68">
@@ -2534,7 +2534,7 @@
         <v>2012</v>
       </c>
       <c r="G68" t="n">
-        <v>6.915313083210559</v>
+        <v>6.607273860194665</v>
       </c>
     </row>
     <row r="69">
@@ -2565,7 +2565,7 @@
         <v>2012</v>
       </c>
       <c r="G69" t="n">
-        <v>10.42480221725747</v>
+        <v>10.376687182361</v>
       </c>
     </row>
     <row r="70">
@@ -2596,7 +2596,7 @@
         <v>2012</v>
       </c>
       <c r="G70" t="n">
-        <v>9.563028197980573</v>
+        <v>9.831106871872349</v>
       </c>
     </row>
     <row r="71">
@@ -2627,7 +2627,7 @@
         <v>2012</v>
       </c>
       <c r="G71" t="n">
-        <v>11.52102423802414</v>
+        <v>12.11577331602093</v>
       </c>
     </row>
     <row r="72">
@@ -2658,7 +2658,7 @@
         <v>2012</v>
       </c>
       <c r="G72" t="n">
-        <v>14.110052781759</v>
+        <v>12.30595664418419</v>
       </c>
     </row>
     <row r="73">
@@ -2689,7 +2689,7 @@
         <v>2012</v>
       </c>
       <c r="G73" t="n">
-        <v>12.71684424044108</v>
+        <v>14.2704773332315</v>
       </c>
     </row>
     <row r="74">
@@ -2720,7 +2720,7 @@
         <v>2012</v>
       </c>
       <c r="G74" t="n">
-        <v>6.175536168480654</v>
+        <v>6.163348530881702</v>
       </c>
     </row>
     <row r="75">
@@ -2751,7 +2751,7 @@
         <v>2012</v>
       </c>
       <c r="G75" t="n">
-        <v>19.49669471950333</v>
+        <v>19.99086471190178</v>
       </c>
     </row>
     <row r="76">
@@ -2782,7 +2782,7 @@
         <v>2012</v>
       </c>
       <c r="G76" t="n">
-        <v>9.24223526658646</v>
+        <v>9.228364276539271</v>
       </c>
     </row>
     <row r="77">
@@ -2813,7 +2813,7 @@
         <v>2012</v>
       </c>
       <c r="G77" t="n">
-        <v>14.5130737107177</v>
+        <v>14.69944105825197</v>
       </c>
     </row>
     <row r="78">
@@ -2844,7 +2844,7 @@
         <v>2012</v>
       </c>
       <c r="G78" t="n">
-        <v>9.498627586108178</v>
+        <v>9.97469162319131</v>
       </c>
     </row>
     <row r="79">
@@ -2875,7 +2875,7 @@
         <v>2012</v>
       </c>
       <c r="G79" t="n">
-        <v>2.073066086474656</v>
+        <v>2.020870005212266</v>
       </c>
     </row>
     <row r="80">
@@ -2906,7 +2906,7 @@
         <v>2012</v>
       </c>
       <c r="G80" t="n">
-        <v>14.91813131979412</v>
+        <v>14.54488697414247</v>
       </c>
     </row>
     <row r="81">
@@ -2937,7 +2937,7 @@
         <v>2012</v>
       </c>
       <c r="G81" t="n">
-        <v>5.261167212315333</v>
+        <v>4.829833788959821</v>
       </c>
     </row>
     <row r="82">
@@ -2968,7 +2968,7 @@
         <v>2012</v>
       </c>
       <c r="G82" t="n">
-        <v>15.94713648569819</v>
+        <v>15.82879218721978</v>
       </c>
     </row>
     <row r="83">
@@ -2999,7 +2999,7 @@
         <v>2012</v>
       </c>
       <c r="G83" t="n">
-        <v>9.062765137084732</v>
+        <v>9.066570728049099</v>
       </c>
     </row>
     <row r="84">
@@ -3030,7 +3030,7 @@
         <v>2012</v>
       </c>
       <c r="G84" t="n">
-        <v>8.051371750511292</v>
+        <v>9.203300004151075</v>
       </c>
     </row>
     <row r="85">
@@ -3061,7 +3061,7 @@
         <v>2012</v>
       </c>
       <c r="G85" t="n">
-        <v>13.26609706492629</v>
+        <v>13.89402970957715</v>
       </c>
     </row>
     <row r="86">
@@ -3092,7 +3092,7 @@
         <v>2012</v>
       </c>
       <c r="G86" t="n">
-        <v>17.93044923951486</v>
+        <v>18.09387508094609</v>
       </c>
     </row>
     <row r="87">
@@ -3123,7 +3123,7 @@
         <v>2012</v>
       </c>
       <c r="G87" t="n">
-        <v>15.64136514900701</v>
+        <v>15.95806741043698</v>
       </c>
     </row>
     <row r="88">
@@ -3154,7 +3154,7 @@
         <v>2012</v>
       </c>
       <c r="G88" t="n">
-        <v>5.934448472107754</v>
+        <v>7.312682984461927</v>
       </c>
     </row>
     <row r="89">
@@ -3185,7 +3185,7 @@
         <v>2012</v>
       </c>
       <c r="G89" t="n">
-        <v>9.535511416899244</v>
+        <v>9.456497210626145</v>
       </c>
     </row>
     <row r="90">
@@ -3216,7 +3216,7 @@
         <v>2012</v>
       </c>
       <c r="G90" t="n">
-        <v>7.418177598504727</v>
+        <v>8.613733377798297</v>
       </c>
     </row>
     <row r="91">
@@ -3247,7 +3247,7 @@
         <v>2012</v>
       </c>
       <c r="G91" t="n">
-        <v>3.227338144508581</v>
+        <v>2.411730016435307</v>
       </c>
     </row>
     <row r="92">
@@ -3278,7 +3278,7 @@
         <v>2012</v>
       </c>
       <c r="G92" t="n">
-        <v>20.3203934966694</v>
+        <v>18.75124898564892</v>
       </c>
     </row>
     <row r="93">
@@ -3309,7 +3309,7 @@
         <v>2012</v>
       </c>
       <c r="G93" t="n">
-        <v>6.511315486406047</v>
+        <v>6.705298756389677</v>
       </c>
     </row>
     <row r="94">
@@ -3340,7 +3340,7 @@
         <v>2012</v>
       </c>
       <c r="G94" t="n">
-        <v>5.243244575785646</v>
+        <v>4.289874548303282</v>
       </c>
     </row>
     <row r="95">
@@ -3371,7 +3371,7 @@
         <v>2013</v>
       </c>
       <c r="G95" t="n">
-        <v>8.994998459668805</v>
+        <v>9.696382959787606</v>
       </c>
     </row>
     <row r="96">
@@ -3402,7 +3402,7 @@
         <v>2013</v>
       </c>
       <c r="G96" t="n">
-        <v>6.539345750693366</v>
+        <v>6.586762073391501</v>
       </c>
     </row>
     <row r="97">
@@ -3433,7 +3433,7 @@
         <v>2013</v>
       </c>
       <c r="G97" t="n">
-        <v>13.25884450499189</v>
+        <v>13.29385639270657</v>
       </c>
     </row>
     <row r="98">
@@ -3464,7 +3464,7 @@
         <v>2013</v>
       </c>
       <c r="G98" t="n">
-        <v>13.74672413460502</v>
+        <v>13.75146871659538</v>
       </c>
     </row>
     <row r="99">
@@ -3495,7 +3495,7 @@
         <v>2013</v>
       </c>
       <c r="G99" t="n">
-        <v>10.905811707226</v>
+        <v>10.90517788981389</v>
       </c>
     </row>
     <row r="100">
@@ -3526,7 +3526,7 @@
         <v>2013</v>
       </c>
       <c r="G100" t="n">
-        <v>15.78004674874852</v>
+        <v>15.8378847167307</v>
       </c>
     </row>
     <row r="101">
@@ -3557,7 +3557,7 @@
         <v>2013</v>
       </c>
       <c r="G101" t="n">
-        <v>10.49363299475215</v>
+        <v>11.23098246786647</v>
       </c>
     </row>
     <row r="102">
@@ -3588,7 +3588,7 @@
         <v>2013</v>
       </c>
       <c r="G102" t="n">
-        <v>8.555196100139216</v>
+        <v>10.3867415264637</v>
       </c>
     </row>
     <row r="103">
@@ -3619,7 +3619,7 @@
         <v>2013</v>
       </c>
       <c r="G103" t="n">
-        <v>14.19005867975948</v>
+        <v>11.63394769835872</v>
       </c>
     </row>
     <row r="104">
@@ -3650,7 +3650,7 @@
         <v>2013</v>
       </c>
       <c r="G104" t="n">
-        <v>16.17091844636681</v>
+        <v>16.44304130444966</v>
       </c>
     </row>
     <row r="105">
@@ -3681,7 +3681,7 @@
         <v>2013</v>
       </c>
       <c r="G105" t="n">
-        <v>2.948516615085651</v>
+        <v>2.273165581775261</v>
       </c>
     </row>
     <row r="106">
@@ -3712,7 +3712,7 @@
         <v>2013</v>
       </c>
       <c r="G106" t="n">
-        <v>17.85129041622964</v>
+        <v>17.84973253293388</v>
       </c>
     </row>
     <row r="107">
@@ -3743,7 +3743,7 @@
         <v>2013</v>
       </c>
       <c r="G107" t="n">
-        <v>9.496693746680801</v>
+        <v>9.156245013216857</v>
       </c>
     </row>
     <row r="108">
@@ -3774,7 +3774,7 @@
         <v>2013</v>
       </c>
       <c r="G108" t="n">
-        <v>11.50004050904674</v>
+        <v>11.64749309062878</v>
       </c>
     </row>
     <row r="109">
@@ -3805,7 +3805,7 @@
         <v>2013</v>
       </c>
       <c r="G109" t="n">
-        <v>13.53303417213813</v>
+        <v>15.01399826088616</v>
       </c>
     </row>
     <row r="110">
@@ -3836,7 +3836,7 @@
         <v>2013</v>
       </c>
       <c r="G110" t="n">
-        <v>1.854704367794537</v>
+        <v>2.116014175921601</v>
       </c>
     </row>
     <row r="111">
@@ -3867,7 +3867,7 @@
         <v>2013</v>
       </c>
       <c r="G111" t="n">
-        <v>10.93643608219021</v>
+        <v>13.36260715413119</v>
       </c>
     </row>
     <row r="112">
@@ -3898,7 +3898,7 @@
         <v>2013</v>
       </c>
       <c r="G112" t="n">
-        <v>0.320455318286717</v>
+        <v>0.2341477651362529</v>
       </c>
     </row>
     <row r="113">
@@ -3929,7 +3929,7 @@
         <v>2013</v>
       </c>
       <c r="G113" t="n">
-        <v>11.08534578466618</v>
+        <v>12.52123300639639</v>
       </c>
     </row>
     <row r="114">
@@ -3960,7 +3960,7 @@
         <v>2013</v>
       </c>
       <c r="G114" t="n">
-        <v>7.514494734819567</v>
+        <v>7.656828665066488</v>
       </c>
     </row>
     <row r="115">
@@ -3991,7 +3991,7 @@
         <v>2013</v>
       </c>
       <c r="G115" t="n">
-        <v>8.437750684503129</v>
+        <v>9.586155671439272</v>
       </c>
     </row>
     <row r="116">
@@ -4022,7 +4022,7 @@
         <v>2013</v>
       </c>
       <c r="G116" t="n">
-        <v>11.04818156517143</v>
+        <v>11.85687401886255</v>
       </c>
     </row>
     <row r="117">
@@ -4053,7 +4053,7 @@
         <v>2013</v>
       </c>
       <c r="G117" t="n">
-        <v>15.89682221900268</v>
+        <v>16.20392251630901</v>
       </c>
     </row>
     <row r="118">
@@ -4084,7 +4084,7 @@
         <v>2013</v>
       </c>
       <c r="G118" t="n">
-        <v>17.08022410756998</v>
+        <v>18.43012697712933</v>
       </c>
     </row>
     <row r="119">
@@ -4115,7 +4115,7 @@
         <v>2013</v>
       </c>
       <c r="G119" t="n">
-        <v>8.885999320609081</v>
+        <v>9.841375962643548</v>
       </c>
     </row>
     <row r="120">
@@ -4146,7 +4146,7 @@
         <v>2013</v>
       </c>
       <c r="G120" t="n">
-        <v>7.598625063055876</v>
+        <v>8.38985288581744</v>
       </c>
     </row>
     <row r="121">
@@ -4177,7 +4177,7 @@
         <v>2013</v>
       </c>
       <c r="G121" t="n">
-        <v>2.407462440341542</v>
+        <v>4.13728139727051</v>
       </c>
     </row>
     <row r="122">
@@ -4208,7 +4208,7 @@
         <v>2013</v>
       </c>
       <c r="G122" t="n">
-        <v>6.105991476939187</v>
+        <v>4.63998900358331</v>
       </c>
     </row>
     <row r="123">
@@ -4239,7 +4239,7 @@
         <v>2013</v>
       </c>
       <c r="G123" t="n">
-        <v>9.682824900257799</v>
+        <v>8.041706917918944</v>
       </c>
     </row>
     <row r="124">
@@ -4270,7 +4270,7 @@
         <v>2013</v>
       </c>
       <c r="G124" t="n">
-        <v>7.373260416680968</v>
+        <v>8.097657845579882</v>
       </c>
     </row>
     <row r="125">
@@ -4301,7 +4301,7 @@
         <v>2013</v>
       </c>
       <c r="G125" t="n">
-        <v>4.818302501395634</v>
+        <v>4.072956177904338</v>
       </c>
     </row>
     <row r="126">
@@ -4332,7 +4332,7 @@
         <v>2014</v>
       </c>
       <c r="G126" t="n">
-        <v>8.30548428656113</v>
+        <v>9.412410074280704</v>
       </c>
     </row>
     <row r="127">
@@ -4363,7 +4363,7 @@
         <v>2014</v>
       </c>
       <c r="G127" t="n">
-        <v>5.98430740629475</v>
+        <v>7.6338136286053</v>
       </c>
     </row>
     <row r="128">
@@ -4394,7 +4394,7 @@
         <v>2014</v>
       </c>
       <c r="G128" t="n">
-        <v>17.61407583471327</v>
+        <v>18.14002575129947</v>
       </c>
     </row>
     <row r="129">
@@ -4425,7 +4425,7 @@
         <v>2014</v>
       </c>
       <c r="G129" t="n">
-        <v>12.94251226738266</v>
+        <v>12.58136091129853</v>
       </c>
     </row>
     <row r="130">
@@ -4456,7 +4456,7 @@
         <v>2014</v>
       </c>
       <c r="G130" t="n">
-        <v>7.114699047871945</v>
+        <v>6.787936841530715</v>
       </c>
     </row>
     <row r="131">
@@ -4487,7 +4487,7 @@
         <v>2014</v>
       </c>
       <c r="G131" t="n">
-        <v>8.965261362172322</v>
+        <v>9.637161957660979</v>
       </c>
     </row>
     <row r="132">
@@ -4518,7 +4518,7 @@
         <v>2014</v>
       </c>
       <c r="G132" t="n">
-        <v>9.433815383312208</v>
+        <v>9.45174277147029</v>
       </c>
     </row>
     <row r="133">
@@ -4549,7 +4549,7 @@
         <v>2014</v>
       </c>
       <c r="G133" t="n">
-        <v>9.629780094920939</v>
+        <v>8.892728945943066</v>
       </c>
     </row>
     <row r="134">
@@ -4580,7 +4580,7 @@
         <v>2014</v>
       </c>
       <c r="G134" t="n">
-        <v>13.5282099150547</v>
+        <v>11.93483998755159</v>
       </c>
     </row>
     <row r="135">
@@ -4611,7 +4611,7 @@
         <v>2014</v>
       </c>
       <c r="G135" t="n">
-        <v>11.64924528847409</v>
+        <v>12.20610196514914</v>
       </c>
     </row>
     <row r="136">
@@ -4642,7 +4642,7 @@
         <v>2014</v>
       </c>
       <c r="G136" t="n">
-        <v>0.9346748641651534</v>
+        <v>0.7741648995230374</v>
       </c>
     </row>
     <row r="137">
@@ -4673,7 +4673,7 @@
         <v>2014</v>
       </c>
       <c r="G137" t="n">
-        <v>23.90569046141808</v>
+        <v>23.33698891901206</v>
       </c>
     </row>
     <row r="138">
@@ -4704,7 +4704,7 @@
         <v>2014</v>
       </c>
       <c r="G138" t="n">
-        <v>11.62128680856064</v>
+        <v>11.85087739889179</v>
       </c>
     </row>
     <row r="139">
@@ -4735,7 +4735,7 @@
         <v>2014</v>
       </c>
       <c r="G139" t="n">
-        <v>11.7011887114345</v>
+        <v>12.76801655157946</v>
       </c>
     </row>
     <row r="140">
@@ -4766,7 +4766,7 @@
         <v>2014</v>
       </c>
       <c r="G140" t="n">
-        <v>15.74065903873748</v>
+        <v>15.57326421672457</v>
       </c>
     </row>
     <row r="141">
@@ -4797,7 +4797,7 @@
         <v>2014</v>
       </c>
       <c r="G141" t="n">
-        <v>6.542397812111702</v>
+        <v>7.027030090931956</v>
       </c>
     </row>
     <row r="142">
@@ -4828,7 +4828,7 @@
         <v>2014</v>
       </c>
       <c r="G142" t="n">
-        <v>11.39731519855702</v>
+        <v>11.95948391309266</v>
       </c>
     </row>
     <row r="143">
@@ -4859,7 +4859,7 @@
         <v>2014</v>
       </c>
       <c r="G143" t="n">
-        <v>1.840429871677791</v>
+        <v>3.253244814385872</v>
       </c>
     </row>
     <row r="144">
@@ -4890,7 +4890,7 @@
         <v>2014</v>
       </c>
       <c r="G144" t="n">
-        <v>12.43342623305061</v>
+        <v>12.77927385420747</v>
       </c>
     </row>
     <row r="145">
@@ -4921,7 +4921,7 @@
         <v>2014</v>
       </c>
       <c r="G145" t="n">
-        <v>5.401738320499247</v>
+        <v>5.251560876684165</v>
       </c>
     </row>
     <row r="146">
@@ -4952,7 +4952,7 @@
         <v>2014</v>
       </c>
       <c r="G146" t="n">
-        <v>8.843215362619414</v>
+        <v>9.780190130151226</v>
       </c>
     </row>
     <row r="147">
@@ -4983,7 +4983,7 @@
         <v>2014</v>
       </c>
       <c r="G147" t="n">
-        <v>13.47394422057949</v>
+        <v>14.68631875214007</v>
       </c>
     </row>
     <row r="148">
@@ -5014,7 +5014,7 @@
         <v>2014</v>
       </c>
       <c r="G148" t="n">
-        <v>16.53710219341107</v>
+        <v>18.40406686367454</v>
       </c>
     </row>
     <row r="149">
@@ -5045,7 +5045,7 @@
         <v>2014</v>
       </c>
       <c r="G149" t="n">
-        <v>14.83272659137242</v>
+        <v>14.62673355942737</v>
       </c>
     </row>
     <row r="150">
@@ -5076,7 +5076,7 @@
         <v>2014</v>
       </c>
       <c r="G150" t="n">
-        <v>8.411559854894232</v>
+        <v>9.425371050427549</v>
       </c>
     </row>
     <row r="151">
@@ -5107,7 +5107,7 @@
         <v>2014</v>
       </c>
       <c r="G151" t="n">
-        <v>4.121643953298049</v>
+        <v>5.123271503477085</v>
       </c>
     </row>
     <row r="152">
@@ -5138,7 +5138,7 @@
         <v>2014</v>
       </c>
       <c r="G152" t="n">
-        <v>2.04423533072948</v>
+        <v>1.871840413522068</v>
       </c>
     </row>
     <row r="153">
@@ -5169,7 +5169,7 @@
         <v>2014</v>
       </c>
       <c r="G153" t="n">
-        <v>9.152483673090426</v>
+        <v>8.754258416109478</v>
       </c>
     </row>
     <row r="154">
@@ -5200,7 +5200,7 @@
         <v>2014</v>
       </c>
       <c r="G154" t="n">
-        <v>8.950548261279948</v>
+        <v>7.835878909742244</v>
       </c>
     </row>
     <row r="155">
@@ -5231,7 +5231,7 @@
         <v>2014</v>
       </c>
       <c r="G155" t="n">
-        <v>7.053421963829715</v>
+        <v>7.621068184112836</v>
       </c>
     </row>
     <row r="156">
@@ -5262,7 +5262,7 @@
         <v>2014</v>
       </c>
       <c r="G156" t="n">
-        <v>7.387762374030797</v>
+        <v>7.044826580058182</v>
       </c>
     </row>
     <row r="157">
@@ -5293,7 +5293,7 @@
         <v>2015</v>
       </c>
       <c r="G157" t="n">
-        <v>7.88393079891707</v>
+        <v>8.206896356091162</v>
       </c>
     </row>
     <row r="158">
@@ -5324,7 +5324,7 @@
         <v>2015</v>
       </c>
       <c r="G158" t="n">
-        <v>7.47151694240509</v>
+        <v>8.221436752469049</v>
       </c>
     </row>
     <row r="159">
@@ -5355,7 +5355,7 @@
         <v>2015</v>
       </c>
       <c r="G159" t="n">
-        <v>14.10048149313454</v>
+        <v>13.7741343283171</v>
       </c>
     </row>
     <row r="160">
@@ -5386,7 +5386,7 @@
         <v>2015</v>
       </c>
       <c r="G160" t="n">
-        <v>11.83263083696822</v>
+        <v>11.97207748174984</v>
       </c>
     </row>
     <row r="161">
@@ -5417,7 +5417,7 @@
         <v>2015</v>
       </c>
       <c r="G161" t="n">
-        <v>7.326151266528376</v>
+        <v>6.325030717589952</v>
       </c>
     </row>
     <row r="162">
@@ -5448,7 +5448,7 @@
         <v>2015</v>
       </c>
       <c r="G162" t="n">
-        <v>8.124112043301835</v>
+        <v>9.598562241720671</v>
       </c>
     </row>
     <row r="163">
@@ -5479,7 +5479,7 @@
         <v>2015</v>
       </c>
       <c r="G163" t="n">
-        <v>4.221859489064441</v>
+        <v>4.203275857529079</v>
       </c>
     </row>
     <row r="164">
@@ -5510,7 +5510,7 @@
         <v>2015</v>
       </c>
       <c r="G164" t="n">
-        <v>9.752712821642923</v>
+        <v>9.336016115085515</v>
       </c>
     </row>
     <row r="165">
@@ -5541,7 +5541,7 @@
         <v>2015</v>
       </c>
       <c r="G165" t="n">
-        <v>14.06339059219667</v>
+        <v>12.57170513177038</v>
       </c>
     </row>
     <row r="166">
@@ -5572,7 +5572,7 @@
         <v>2015</v>
       </c>
       <c r="G166" t="n">
-        <v>11.84254523534939</v>
+        <v>12.06107268699509</v>
       </c>
     </row>
     <row r="167">
@@ -5603,7 +5603,7 @@
         <v>2015</v>
       </c>
       <c r="G167" t="n">
-        <v>1.003380179819061</v>
+        <v>0.7670525609111774</v>
       </c>
     </row>
     <row r="168">
@@ -5634,7 +5634,7 @@
         <v>2015</v>
       </c>
       <c r="G168" t="n">
-        <v>25.67356093829854</v>
+        <v>24.87666205627959</v>
       </c>
     </row>
     <row r="169">
@@ -5665,7 +5665,7 @@
         <v>2015</v>
       </c>
       <c r="G169" t="n">
-        <v>9.021744495933779</v>
+        <v>10.06499438250761</v>
       </c>
     </row>
     <row r="170">
@@ -5696,7 +5696,7 @@
         <v>2015</v>
       </c>
       <c r="G170" t="n">
-        <v>8.907388257899274</v>
+        <v>9.027827595413584</v>
       </c>
     </row>
     <row r="171">
@@ -5727,7 +5727,7 @@
         <v>2015</v>
       </c>
       <c r="G171" t="n">
-        <v>10.55769822419848</v>
+        <v>10.33602513873777</v>
       </c>
     </row>
     <row r="172">
@@ -5758,7 +5758,7 @@
         <v>2015</v>
       </c>
       <c r="G172" t="n">
-        <v>4.063997660595211</v>
+        <v>4.677096579360915</v>
       </c>
     </row>
     <row r="173">
@@ -5789,7 +5789,7 @@
         <v>2015</v>
       </c>
       <c r="G173" t="n">
-        <v>6.502845779210439</v>
+        <v>7.938153674203694</v>
       </c>
     </row>
     <row r="174">
@@ -5820,7 +5820,7 @@
         <v>2015</v>
       </c>
       <c r="G174" t="n">
-        <v>2.773381668235749</v>
+        <v>4.304602777874742</v>
       </c>
     </row>
     <row r="175">
@@ -5851,7 +5851,7 @@
         <v>2015</v>
       </c>
       <c r="G175" t="n">
-        <v>14.14997386629757</v>
+        <v>14.45386158823227</v>
       </c>
     </row>
     <row r="176">
@@ -5882,7 +5882,7 @@
         <v>2015</v>
       </c>
       <c r="G176" t="n">
-        <v>7.106054425569595</v>
+        <v>7.980574548429114</v>
       </c>
     </row>
     <row r="177">
@@ -5913,7 +5913,7 @@
         <v>2015</v>
       </c>
       <c r="G177" t="n">
-        <v>8.814384852131228</v>
+        <v>9.634036011904213</v>
       </c>
     </row>
     <row r="178">
@@ -5944,7 +5944,7 @@
         <v>2015</v>
       </c>
       <c r="G178" t="n">
-        <v>16.04093491012113</v>
+        <v>16.15421983626184</v>
       </c>
     </row>
     <row r="179">
@@ -5975,7 +5975,7 @@
         <v>2015</v>
       </c>
       <c r="G179" t="n">
-        <v>15.46324580409485</v>
+        <v>15.58923722570786</v>
       </c>
     </row>
     <row r="180">
@@ -6006,7 +6006,7 @@
         <v>2015</v>
       </c>
       <c r="G180" t="n">
-        <v>14.60027322724892</v>
+        <v>14.383105565941</v>
       </c>
     </row>
     <row r="181">
@@ -6037,7 +6037,7 @@
         <v>2015</v>
       </c>
       <c r="G181" t="n">
-        <v>10.6679525896341</v>
+        <v>11.41531152655703</v>
       </c>
     </row>
     <row r="182">
@@ -6068,7 +6068,7 @@
         <v>2015</v>
       </c>
       <c r="G182" t="n">
-        <v>3.891664338993093</v>
+        <v>3.659699079832164</v>
       </c>
     </row>
     <row r="183">
@@ -6099,7 +6099,7 @@
         <v>2015</v>
       </c>
       <c r="G183" t="n">
-        <v>2.798497608744011</v>
+        <v>3.177500407900542</v>
       </c>
     </row>
     <row r="184">
@@ -6130,7 +6130,7 @@
         <v>2015</v>
       </c>
       <c r="G184" t="n">
-        <v>7.538285394606372</v>
+        <v>7.460887088703498</v>
       </c>
     </row>
     <row r="185">
@@ -6161,7 +6161,7 @@
         <v>2015</v>
       </c>
       <c r="G185" t="n">
-        <v>13.29943572993426</v>
+        <v>11.80246200560098</v>
       </c>
     </row>
     <row r="186">
@@ -6192,7 +6192,7 @@
         <v>2015</v>
       </c>
       <c r="G186" t="n">
-        <v>4.888946688940908</v>
+        <v>5.08997926771158</v>
       </c>
     </row>
     <row r="187">
@@ -6223,7 +6223,7 @@
         <v>2015</v>
       </c>
       <c r="G187" t="n">
-        <v>7.929036854303676</v>
+        <v>7.582440550149951</v>
       </c>
     </row>
     <row r="188">
@@ -6254,7 +6254,7 @@
         <v>2016</v>
       </c>
       <c r="G188" t="n">
-        <v>6.769259907480745</v>
+        <v>7.64459525884634</v>
       </c>
     </row>
     <row r="189">
@@ -6285,7 +6285,7 @@
         <v>2016</v>
       </c>
       <c r="G189" t="n">
-        <v>8.395319836054256</v>
+        <v>9.005748959397023</v>
       </c>
     </row>
     <row r="190">
@@ -6316,7 +6316,7 @@
         <v>2016</v>
       </c>
       <c r="G190" t="n">
-        <v>12.18066735314034</v>
+        <v>12.08548768478376</v>
       </c>
     </row>
     <row r="191">
@@ -6347,7 +6347,7 @@
         <v>2016</v>
       </c>
       <c r="G191" t="n">
-        <v>11.92029645700293</v>
+        <v>12.12000332465605</v>
       </c>
     </row>
     <row r="192">
@@ -6378,7 +6378,7 @@
         <v>2016</v>
       </c>
       <c r="G192" t="n">
-        <v>1.821899942230051</v>
+        <v>2.348555332682928</v>
       </c>
     </row>
     <row r="193">
@@ -6409,7 +6409,7 @@
         <v>2016</v>
       </c>
       <c r="G193" t="n">
-        <v>8.671568926770187</v>
+        <v>9.928907460203213</v>
       </c>
     </row>
     <row r="194">
@@ -6440,7 +6440,7 @@
         <v>2016</v>
       </c>
       <c r="G194" t="n">
-        <v>2.697985678423223</v>
+        <v>3.233999291424413</v>
       </c>
     </row>
     <row r="195">
@@ -6471,7 +6471,7 @@
         <v>2016</v>
       </c>
       <c r="G195" t="n">
-        <v>2.78774127000872</v>
+        <v>2.64798562868531</v>
       </c>
     </row>
     <row r="196">
@@ -6502,7 +6502,7 @@
         <v>2016</v>
       </c>
       <c r="G196" t="n">
-        <v>11.77802406430891</v>
+        <v>12.71471504899215</v>
       </c>
     </row>
     <row r="197">
@@ -6533,7 +6533,7 @@
         <v>2016</v>
       </c>
       <c r="G197" t="n">
-        <v>9.602464005442453</v>
+        <v>11.23781129415234</v>
       </c>
     </row>
     <row r="198">
@@ -6564,7 +6564,7 @@
         <v>2016</v>
       </c>
       <c r="G198" t="n">
-        <v>0.3263418435603924</v>
+        <v>0.1132417654991327</v>
       </c>
     </row>
     <row r="199">
@@ -6595,7 +6595,7 @@
         <v>2016</v>
       </c>
       <c r="G199" t="n">
-        <v>23.29188542373261</v>
+        <v>23.7508292862921</v>
       </c>
     </row>
     <row r="200">
@@ -6626,7 +6626,7 @@
         <v>2016</v>
       </c>
       <c r="G200" t="n">
-        <v>8.643224398533892</v>
+        <v>8.98049275908566</v>
       </c>
     </row>
     <row r="201">
@@ -6657,7 +6657,7 @@
         <v>2016</v>
       </c>
       <c r="G201" t="n">
-        <v>9.030290916757995</v>
+        <v>9.62914108001873</v>
       </c>
     </row>
     <row r="202">
@@ -6688,7 +6688,7 @@
         <v>2016</v>
       </c>
       <c r="G202" t="n">
-        <v>5.652668401638987</v>
+        <v>5.4286729534085</v>
       </c>
     </row>
     <row r="203">
@@ -6719,7 +6719,7 @@
         <v>2016</v>
       </c>
       <c r="G203" t="n">
-        <v>4.224736227362635</v>
+        <v>4.783415216319405</v>
       </c>
     </row>
     <row r="204">
@@ -6750,7 +6750,7 @@
         <v>2016</v>
       </c>
       <c r="G204" t="n">
-        <v>7.601529539742352</v>
+        <v>9.571647572198085</v>
       </c>
     </row>
     <row r="205">
@@ -6781,7 +6781,7 @@
         <v>2016</v>
       </c>
       <c r="G205" t="n">
-        <v>3.789894108517557</v>
+        <v>4.281491532451831</v>
       </c>
     </row>
     <row r="206">
@@ -6812,7 +6812,7 @@
         <v>2016</v>
       </c>
       <c r="G206" t="n">
-        <v>11.99431832383077</v>
+        <v>14.16611086815648</v>
       </c>
     </row>
     <row r="207">
@@ -6843,7 +6843,7 @@
         <v>2016</v>
       </c>
       <c r="G207" t="n">
-        <v>18.25363266144826</v>
+        <v>19.19853514416969</v>
       </c>
     </row>
     <row r="208">
@@ -6874,7 +6874,7 @@
         <v>2016</v>
       </c>
       <c r="G208" t="n">
-        <v>10.05696316074129</v>
+        <v>10.39427762200415</v>
       </c>
     </row>
     <row r="209">
@@ -6905,7 +6905,7 @@
         <v>2016</v>
       </c>
       <c r="G209" t="n">
-        <v>13.50124405426109</v>
+        <v>13.89730449729396</v>
       </c>
     </row>
     <row r="210">
@@ -6936,7 +6936,7 @@
         <v>2016</v>
       </c>
       <c r="G210" t="n">
-        <v>12.75129390851688</v>
+        <v>13.27338346043497</v>
       </c>
     </row>
     <row r="211">
@@ -6967,7 +6967,7 @@
         <v>2016</v>
       </c>
       <c r="G211" t="n">
-        <v>21.44626095497471</v>
+        <v>22.01535081014253</v>
       </c>
     </row>
     <row r="212">
@@ -6998,7 +6998,7 @@
         <v>2016</v>
       </c>
       <c r="G212" t="n">
-        <v>11.31476588314212</v>
+        <v>12.37682738921613</v>
       </c>
     </row>
     <row r="213">
@@ -7029,7 +7029,7 @@
         <v>2016</v>
       </c>
       <c r="G213" t="n">
-        <v>3.40387785365632</v>
+        <v>3.589167227807831</v>
       </c>
     </row>
     <row r="214">
@@ -7060,7 +7060,7 @@
         <v>2016</v>
       </c>
       <c r="G214" t="n">
-        <v>6.398615189125978</v>
+        <v>6.632596361394443</v>
       </c>
     </row>
     <row r="215">
@@ -7091,7 +7091,7 @@
         <v>2016</v>
       </c>
       <c r="G215" t="n">
-        <v>6.37622617562459</v>
+        <v>5.584188055583113</v>
       </c>
     </row>
     <row r="216">
@@ -7122,7 +7122,7 @@
         <v>2016</v>
       </c>
       <c r="G216" t="n">
-        <v>16.37201260711674</v>
+        <v>15.29513809129406</v>
       </c>
     </row>
     <row r="217">
@@ -7153,7 +7153,7 @@
         <v>2016</v>
       </c>
       <c r="G217" t="n">
-        <v>6.745676337986815</v>
+        <v>7.312798428429113</v>
       </c>
     </row>
     <row r="218">
@@ -7184,7 +7184,7 @@
         <v>2016</v>
       </c>
       <c r="G218" t="n">
-        <v>5.896274071044512</v>
+        <v>6.220779653905655</v>
       </c>
     </row>
     <row r="219">
@@ -7215,7 +7215,7 @@
         <v>2017</v>
       </c>
       <c r="G219" t="n">
-        <v>5.785457086042887</v>
+        <v>6.050264563189806</v>
       </c>
     </row>
     <row r="220">
@@ -7246,7 +7246,7 @@
         <v>2017</v>
       </c>
       <c r="G220" t="n">
-        <v>6.289395539736913</v>
+        <v>6.859967448309121</v>
       </c>
     </row>
     <row r="221">
@@ -7277,7 +7277,7 @@
         <v>2017</v>
       </c>
       <c r="G221" t="n">
-        <v>14.18256151729862</v>
+        <v>15.23630942317446</v>
       </c>
     </row>
     <row r="222">
@@ -7308,7 +7308,7 @@
         <v>2017</v>
       </c>
       <c r="G222" t="n">
-        <v>11.30645704660303</v>
+        <v>12.45951712521056</v>
       </c>
     </row>
     <row r="223">
@@ -7339,7 +7339,7 @@
         <v>2017</v>
       </c>
       <c r="G223" t="n">
-        <v>2.10745310241702</v>
+        <v>2.911375945828353</v>
       </c>
     </row>
     <row r="224">
@@ -7370,7 +7370,7 @@
         <v>2017</v>
       </c>
       <c r="G224" t="n">
-        <v>13.51392052056705</v>
+        <v>14.50281199163374</v>
       </c>
     </row>
     <row r="225">
@@ -7401,7 +7401,7 @@
         <v>2017</v>
       </c>
       <c r="G225" t="n">
-        <v>2.426623196804851</v>
+        <v>2.447178122707198</v>
       </c>
     </row>
     <row r="226">
@@ -7432,7 +7432,7 @@
         <v>2017</v>
       </c>
       <c r="G226" t="n">
-        <v>2.256573441894042</v>
+        <v>2.765496658058909</v>
       </c>
     </row>
     <row r="227">
@@ -7463,7 +7463,7 @@
         <v>2017</v>
       </c>
       <c r="G227" t="n">
-        <v>12.9598479552604</v>
+        <v>12.53317786613072</v>
       </c>
     </row>
     <row r="228">
@@ -7494,7 +7494,7 @@
         <v>2017</v>
       </c>
       <c r="G228" t="n">
-        <v>8.312670050470878</v>
+        <v>7.674067290415031</v>
       </c>
     </row>
     <row r="229">
@@ -7556,7 +7556,7 @@
         <v>2017</v>
       </c>
       <c r="G230" t="n">
-        <v>20.99239978657302</v>
+        <v>21.34501828226968</v>
       </c>
     </row>
     <row r="231">
@@ -7587,7 +7587,7 @@
         <v>2017</v>
       </c>
       <c r="G231" t="n">
-        <v>5.819688378112624</v>
+        <v>7.027621560907738</v>
       </c>
     </row>
     <row r="232">
@@ -7618,7 +7618,7 @@
         <v>2017</v>
       </c>
       <c r="G232" t="n">
-        <v>11.32784544699854</v>
+        <v>11.12558325938225</v>
       </c>
     </row>
     <row r="233">
@@ -7649,7 +7649,7 @@
         <v>2017</v>
       </c>
       <c r="G233" t="n">
-        <v>9.405737350688863</v>
+        <v>9.047260972531937</v>
       </c>
     </row>
     <row r="234">
@@ -7680,7 +7680,7 @@
         <v>2017</v>
       </c>
       <c r="G234" t="n">
-        <v>4.440717248109295</v>
+        <v>4.088192242010246</v>
       </c>
     </row>
     <row r="235">
@@ -7711,7 +7711,7 @@
         <v>2017</v>
       </c>
       <c r="G235" t="n">
-        <v>7.5474155281415</v>
+        <v>8.402986606050561</v>
       </c>
     </row>
     <row r="236">
@@ -7742,7 +7742,7 @@
         <v>2017</v>
       </c>
       <c r="G236" t="n">
-        <v>6.424098655177827</v>
+        <v>6.755071427325531</v>
       </c>
     </row>
     <row r="237">
@@ -7773,7 +7773,7 @@
         <v>2017</v>
       </c>
       <c r="G237" t="n">
-        <v>11.10175327174418</v>
+        <v>12.59045511890113</v>
       </c>
     </row>
     <row r="238">
@@ -7804,7 +7804,7 @@
         <v>2017</v>
       </c>
       <c r="G238" t="n">
-        <v>19.81706175336105</v>
+        <v>19.81279673112052</v>
       </c>
     </row>
     <row r="239">
@@ -7835,7 +7835,7 @@
         <v>2017</v>
       </c>
       <c r="G239" t="n">
-        <v>11.30348210869596</v>
+        <v>13.2387937717469</v>
       </c>
     </row>
     <row r="240">
@@ -7866,7 +7866,7 @@
         <v>2017</v>
       </c>
       <c r="G240" t="n">
-        <v>14.1830072871888</v>
+        <v>14.9101170088044</v>
       </c>
     </row>
     <row r="241">
@@ -7897,7 +7897,7 @@
         <v>2017</v>
       </c>
       <c r="G241" t="n">
-        <v>8.557702227920142</v>
+        <v>8.327928219015499</v>
       </c>
     </row>
     <row r="242">
@@ -7928,7 +7928,7 @@
         <v>2017</v>
       </c>
       <c r="G242" t="n">
-        <v>22.44307089340573</v>
+        <v>23.92953704220179</v>
       </c>
     </row>
     <row r="243">
@@ -7959,7 +7959,7 @@
         <v>2017</v>
       </c>
       <c r="G243" t="n">
-        <v>7.797884798360536</v>
+        <v>8.856278513747592</v>
       </c>
     </row>
     <row r="244">
@@ -7990,7 +7990,7 @@
         <v>2017</v>
       </c>
       <c r="G244" t="n">
-        <v>4.193564710730061</v>
+        <v>4.404020067808373</v>
       </c>
     </row>
     <row r="245">
@@ -8021,7 +8021,7 @@
         <v>2017</v>
       </c>
       <c r="G245" t="n">
-        <v>3.88292455783643</v>
+        <v>4.041378982975756</v>
       </c>
     </row>
     <row r="246">
@@ -8052,7 +8052,7 @@
         <v>2017</v>
       </c>
       <c r="G246" t="n">
-        <v>9.851656032550547</v>
+        <v>9.402797410325896</v>
       </c>
     </row>
     <row r="247">
@@ -8083,7 +8083,7 @@
         <v>2017</v>
       </c>
       <c r="G247" t="n">
-        <v>13.76413922239429</v>
+        <v>13.08639867160497</v>
       </c>
     </row>
     <row r="248">
@@ -8114,7 +8114,7 @@
         <v>2017</v>
       </c>
       <c r="G248" t="n">
-        <v>5.251273615845514</v>
+        <v>5.526354247028796</v>
       </c>
     </row>
     <row r="249">
@@ -8145,7 +8145,7 @@
         <v>2017</v>
       </c>
       <c r="G249" t="n">
-        <v>10.22305343301759</v>
+        <v>9.762708139710561</v>
       </c>
     </row>
     <row r="250">
@@ -8176,7 +8176,7 @@
         <v>2018</v>
       </c>
       <c r="G250" t="n">
-        <v>4.22998772126546</v>
+        <v>4.291744670133128</v>
       </c>
     </row>
     <row r="251">
@@ -8207,7 +8207,7 @@
         <v>2018</v>
       </c>
       <c r="G251" t="n">
-        <v>7.573238209541334</v>
+        <v>6.336560380563701</v>
       </c>
     </row>
     <row r="252">
@@ -8238,7 +8238,7 @@
         <v>2018</v>
       </c>
       <c r="G252" t="n">
-        <v>11.2339648811007</v>
+        <v>11.66927351492208</v>
       </c>
     </row>
     <row r="253">
@@ -8269,7 +8269,7 @@
         <v>2018</v>
       </c>
       <c r="G253" t="n">
-        <v>12.91651182955531</v>
+        <v>14.21404682274247</v>
       </c>
     </row>
     <row r="254">
@@ -8300,7 +8300,7 @@
         <v>2018</v>
       </c>
       <c r="G254" t="n">
-        <v>1.740950870847063</v>
+        <v>1.882664816787652</v>
       </c>
     </row>
     <row r="255">
@@ -8331,7 +8331,7 @@
         <v>2018</v>
       </c>
       <c r="G255" t="n">
-        <v>20.98753950322135</v>
+        <v>21.60646129550507</v>
       </c>
     </row>
     <row r="256">
@@ -8362,7 +8362,7 @@
         <v>2018</v>
       </c>
       <c r="G256" t="n">
-        <v>6.379865296790828</v>
+        <v>5.43671813999472</v>
       </c>
     </row>
     <row r="257">
@@ -8393,7 +8393,7 @@
         <v>2018</v>
       </c>
       <c r="G257" t="n">
-        <v>6.364949515174051</v>
+        <v>5.924458682531964</v>
       </c>
     </row>
     <row r="258">
@@ -8424,7 +8424,7 @@
         <v>2018</v>
       </c>
       <c r="G258" t="n">
-        <v>13.60523470963209</v>
+        <v>13.35907483096931</v>
       </c>
     </row>
     <row r="259">
@@ -8455,7 +8455,7 @@
         <v>2018</v>
       </c>
       <c r="G259" t="n">
-        <v>6.404887130745821</v>
+        <v>5.725960539556182</v>
       </c>
     </row>
     <row r="260">
@@ -8517,7 +8517,7 @@
         <v>2018</v>
       </c>
       <c r="G261" t="n">
-        <v>20.73195362912353</v>
+        <v>20.40618046196759</v>
       </c>
     </row>
     <row r="262">
@@ -8548,7 +8548,7 @@
         <v>2018</v>
       </c>
       <c r="G262" t="n">
-        <v>8.318521016344034</v>
+        <v>8.350146027536622</v>
       </c>
     </row>
     <row r="263">
@@ -8579,7 +8579,7 @@
         <v>2018</v>
       </c>
       <c r="G263" t="n">
-        <v>11.09470100212463</v>
+        <v>11.05750874781585</v>
       </c>
     </row>
     <row r="264">
@@ -8610,7 +8610,7 @@
         <v>2018</v>
       </c>
       <c r="G264" t="n">
-        <v>7.010192380651954</v>
+        <v>6.468815407503399</v>
       </c>
     </row>
     <row r="265">
@@ -8641,7 +8641,7 @@
         <v>2018</v>
       </c>
       <c r="G265" t="n">
-        <v>5.905142334624732</v>
+        <v>6.464614866328176</v>
       </c>
     </row>
     <row r="266">
@@ -8672,7 +8672,7 @@
         <v>2018</v>
       </c>
       <c r="G266" t="n">
-        <v>7.812321885900583</v>
+        <v>7.422845721841824</v>
       </c>
     </row>
     <row r="267">
@@ -8703,7 +8703,7 @@
         <v>2018</v>
       </c>
       <c r="G267" t="n">
-        <v>6.377725197854625</v>
+        <v>6.974617065954404</v>
       </c>
     </row>
     <row r="268">
@@ -8734,7 +8734,7 @@
         <v>2018</v>
       </c>
       <c r="G268" t="n">
-        <v>7.352827649169444</v>
+        <v>6.256104560421302</v>
       </c>
     </row>
     <row r="269">
@@ -8765,7 +8765,7 @@
         <v>2018</v>
       </c>
       <c r="G269" t="n">
-        <v>21.3804000548525</v>
+        <v>22.47693841169259</v>
       </c>
     </row>
     <row r="270">
@@ -8796,7 +8796,7 @@
         <v>2018</v>
       </c>
       <c r="G270" t="n">
-        <v>13.02669589097512</v>
+        <v>12.56348268222129</v>
       </c>
     </row>
     <row r="271">
@@ -8827,7 +8827,7 @@
         <v>2018</v>
       </c>
       <c r="G271" t="n">
-        <v>13.74946882429282</v>
+        <v>13.61130571602486</v>
       </c>
     </row>
     <row r="272">
@@ -8858,7 +8858,7 @@
         <v>2018</v>
       </c>
       <c r="G272" t="n">
-        <v>7.802234162806382</v>
+        <v>8.080317139663673</v>
       </c>
     </row>
     <row r="273">
@@ -8889,7 +8889,7 @@
         <v>2018</v>
       </c>
       <c r="G273" t="n">
-        <v>20.41995337300663</v>
+        <v>20.60021130119941</v>
       </c>
     </row>
     <row r="274">
@@ -8920,7 +8920,7 @@
         <v>2018</v>
       </c>
       <c r="G274" t="n">
-        <v>6.882631294830895</v>
+        <v>7.198219131339063</v>
       </c>
     </row>
     <row r="275">
@@ -8951,7 +8951,7 @@
         <v>2018</v>
       </c>
       <c r="G275" t="n">
-        <v>3.576304385870912</v>
+        <v>3.786221957728478</v>
       </c>
     </row>
     <row r="276">
@@ -8982,7 +8982,7 @@
         <v>2018</v>
       </c>
       <c r="G276" t="n">
-        <v>3.209764461468107</v>
+        <v>3.939537282458599</v>
       </c>
     </row>
     <row r="277">
@@ -9013,7 +9013,7 @@
         <v>2018</v>
       </c>
       <c r="G277" t="n">
-        <v>8.599012166931914</v>
+        <v>8.498849953940702</v>
       </c>
     </row>
     <row r="278">
@@ -9044,7 +9044,7 @@
         <v>2018</v>
       </c>
       <c r="G278" t="n">
-        <v>13.21644315748548</v>
+        <v>13.35745414241529</v>
       </c>
     </row>
     <row r="279">
@@ -9075,7 +9075,7 @@
         <v>2018</v>
       </c>
       <c r="G279" t="n">
-        <v>5.057739880763926</v>
+        <v>5.550755823625056</v>
       </c>
     </row>
     <row r="280">
@@ -9106,7 +9106,7 @@
         <v>2018</v>
       </c>
       <c r="G280" t="n">
-        <v>9.454848664202412</v>
+        <v>10.03272024746781</v>
       </c>
     </row>
     <row r="281">
@@ -9137,7 +9137,7 @@
         <v>2019</v>
       </c>
       <c r="G281" t="n">
-        <v>4.2602771896794</v>
+        <v>4.54889323533869</v>
       </c>
     </row>
     <row r="282">
@@ -9168,7 +9168,7 @@
         <v>2019</v>
       </c>
       <c r="G282" t="n">
-        <v>10.10649610499129</v>
+        <v>8.656112502403039</v>
       </c>
     </row>
     <row r="283">
@@ -9199,7 +9199,7 @@
         <v>2019</v>
       </c>
       <c r="G283" t="n">
-        <v>12.03344684155729</v>
+        <v>12.46589437327471</v>
       </c>
     </row>
     <row r="284">
@@ -9230,7 +9230,7 @@
         <v>2019</v>
       </c>
       <c r="G284" t="n">
-        <v>11.2409589281822</v>
+        <v>10.43608414317965</v>
       </c>
     </row>
     <row r="285">
@@ -9261,7 +9261,7 @@
         <v>2019</v>
       </c>
       <c r="G285" t="n">
-        <v>3.117769220795161</v>
+        <v>3.361889323776712</v>
       </c>
     </row>
     <row r="286">
@@ -9292,7 +9292,7 @@
         <v>2019</v>
       </c>
       <c r="G286" t="n">
-        <v>5.260307549971127</v>
+        <v>6.37503289967283</v>
       </c>
     </row>
     <row r="287">
@@ -9323,7 +9323,7 @@
         <v>2019</v>
       </c>
       <c r="G287" t="n">
-        <v>7.71898600941541</v>
+        <v>7.435771198023266</v>
       </c>
     </row>
     <row r="288">
@@ -9354,7 +9354,7 @@
         <v>2019</v>
       </c>
       <c r="G288" t="n">
-        <v>6.922650086075244</v>
+        <v>7.024863183167835</v>
       </c>
     </row>
     <row r="289">
@@ -9385,7 +9385,7 @@
         <v>2019</v>
       </c>
       <c r="G289" t="n">
-        <v>13.79140767611473</v>
+        <v>13.54052709788554</v>
       </c>
     </row>
     <row r="290">
@@ -9416,7 +9416,7 @@
         <v>2019</v>
       </c>
       <c r="G290" t="n">
-        <v>9.064706681964216</v>
+        <v>9.069744401609578</v>
       </c>
     </row>
     <row r="291">
@@ -9447,7 +9447,7 @@
         <v>2019</v>
       </c>
       <c r="G291" t="n">
-        <v>1.990555760172915</v>
+        <v>1.762618467392699</v>
       </c>
     </row>
     <row r="292">
@@ -9478,7 +9478,7 @@
         <v>2019</v>
       </c>
       <c r="G292" t="n">
-        <v>15.08928953654796</v>
+        <v>14.36506060209913</v>
       </c>
     </row>
     <row r="293">
@@ -9509,7 +9509,7 @@
         <v>2019</v>
       </c>
       <c r="G293" t="n">
-        <v>12.36002523858547</v>
+        <v>12.4183318171909</v>
       </c>
     </row>
     <row r="294">
@@ -9540,7 +9540,7 @@
         <v>2019</v>
       </c>
       <c r="G294" t="n">
-        <v>9.915133149181395</v>
+        <v>8.816148930648444</v>
       </c>
     </row>
     <row r="295">
@@ -9571,7 +9571,7 @@
         <v>2019</v>
       </c>
       <c r="G295" t="n">
-        <v>7.150552250797561</v>
+        <v>7.325669724445729</v>
       </c>
     </row>
     <row r="296">
@@ -9602,7 +9602,7 @@
         <v>2019</v>
       </c>
       <c r="G296" t="n">
-        <v>3.666221206822554</v>
+        <v>3.099543854495249</v>
       </c>
     </row>
     <row r="297">
@@ -9633,7 +9633,7 @@
         <v>2019</v>
       </c>
       <c r="G297" t="n">
-        <v>9.120499929296624</v>
+        <v>10.48325696361492</v>
       </c>
     </row>
     <row r="298">
@@ -9664,7 +9664,7 @@
         <v>2019</v>
       </c>
       <c r="G298" t="n">
-        <v>4.289318847768731</v>
+        <v>4.514972916081847</v>
       </c>
     </row>
     <row r="299">
@@ -9695,7 +9695,7 @@
         <v>2019</v>
       </c>
       <c r="G299" t="n">
-        <v>10.75439762618262</v>
+        <v>12.34968548160033</v>
       </c>
     </row>
     <row r="300">
@@ -9726,7 +9726,7 @@
         <v>2019</v>
       </c>
       <c r="G300" t="n">
-        <v>19.51702992310294</v>
+        <v>19.73235968051396</v>
       </c>
     </row>
     <row r="301">
@@ -9757,7 +9757,7 @@
         <v>2019</v>
       </c>
       <c r="G301" t="n">
-        <v>11.38651977390428</v>
+        <v>12.61466107656021</v>
       </c>
     </row>
     <row r="302">
@@ -9788,7 +9788,7 @@
         <v>2019</v>
       </c>
       <c r="G302" t="n">
-        <v>12.14725465153277</v>
+        <v>12.26756333846978</v>
       </c>
     </row>
     <row r="303">
@@ -9819,7 +9819,7 @@
         <v>2019</v>
       </c>
       <c r="G303" t="n">
-        <v>7.305216343780829</v>
+        <v>9.134406641310976</v>
       </c>
     </row>
     <row r="304">
@@ -9850,7 +9850,7 @@
         <v>2019</v>
       </c>
       <c r="G304" t="n">
-        <v>14.30887306900703</v>
+        <v>15.39940421591108</v>
       </c>
     </row>
     <row r="305">
@@ -9881,7 +9881,7 @@
         <v>2019</v>
       </c>
       <c r="G305" t="n">
-        <v>11.12426368490645</v>
+        <v>10.68565113017613</v>
       </c>
     </row>
     <row r="306">
@@ -9912,7 +9912,7 @@
         <v>2019</v>
       </c>
       <c r="G306" t="n">
-        <v>5.865681115338847</v>
+        <v>6.049687251521172</v>
       </c>
     </row>
     <row r="307">
@@ -9943,7 +9943,7 @@
         <v>2019</v>
       </c>
       <c r="G307" t="n">
-        <v>4.600645977376456</v>
+        <v>4.695753062631032</v>
       </c>
     </row>
     <row r="308">
@@ -9974,7 +9974,7 @@
         <v>2019</v>
       </c>
       <c r="G308" t="n">
-        <v>9.945363695429009</v>
+        <v>8.751178244917122</v>
       </c>
     </row>
     <row r="309">
@@ -10005,7 +10005,7 @@
         <v>2019</v>
       </c>
       <c r="G309" t="n">
-        <v>12.26122994299109</v>
+        <v>11.94015540035137</v>
       </c>
     </row>
     <row r="310">
@@ -10036,7 +10036,7 @@
         <v>2019</v>
       </c>
       <c r="G310" t="n">
-        <v>6.826407267249071</v>
+        <v>7.627650063294405</v>
       </c>
     </row>
     <row r="311">
@@ -10067,7 +10067,7 @@
         <v>2019</v>
       </c>
       <c r="G311" t="n">
-        <v>6.857298915539502</v>
+        <v>5.790886039743818</v>
       </c>
     </row>
     <row r="312">
@@ -10098,7 +10098,7 @@
         <v>2020</v>
       </c>
       <c r="G312" t="n">
-        <v>2.08223168475623</v>
+        <v>1.902452670275612</v>
       </c>
     </row>
     <row r="313">
@@ -10129,7 +10129,7 @@
         <v>2020</v>
       </c>
       <c r="G313" t="n">
-        <v>7.885193062071368</v>
+        <v>7.154721385522141</v>
       </c>
     </row>
     <row r="314">
@@ -10160,7 +10160,7 @@
         <v>2020</v>
       </c>
       <c r="G314" t="n">
-        <v>12.84635490423381</v>
+        <v>12.6227240595791</v>
       </c>
     </row>
     <row r="315">
@@ -10191,7 +10191,7 @@
         <v>2020</v>
       </c>
       <c r="G315" t="n">
-        <v>13.95728886022794</v>
+        <v>15.23354909761737</v>
       </c>
     </row>
     <row r="316">
@@ -10222,7 +10222,7 @@
         <v>2020</v>
       </c>
       <c r="G316" t="n">
-        <v>3.49836740232333</v>
+        <v>3.614353416086489</v>
       </c>
     </row>
     <row r="317">
@@ -10253,7 +10253,7 @@
         <v>2020</v>
       </c>
       <c r="G317" t="n">
-        <v>4.723232096699761</v>
+        <v>4.916290518630091</v>
       </c>
     </row>
     <row r="318">
@@ -10284,7 +10284,7 @@
         <v>2020</v>
       </c>
       <c r="G318" t="n">
-        <v>8.100578191736405</v>
+        <v>9.498066783079937</v>
       </c>
     </row>
     <row r="319">
@@ -10315,7 +10315,7 @@
         <v>2020</v>
       </c>
       <c r="G319" t="n">
-        <v>3.393986861522021</v>
+        <v>3.484993629374127</v>
       </c>
     </row>
     <row r="320">
@@ -10346,7 +10346,7 @@
         <v>2020</v>
       </c>
       <c r="G320" t="n">
-        <v>13.89770451371136</v>
+        <v>15.0135077602001</v>
       </c>
     </row>
     <row r="321">
@@ -10377,7 +10377,7 @@
         <v>2020</v>
       </c>
       <c r="G321" t="n">
-        <v>5.35969127632747</v>
+        <v>4.98009313704057</v>
       </c>
     </row>
     <row r="322">
@@ -10408,7 +10408,7 @@
         <v>2020</v>
       </c>
       <c r="G322" t="n">
-        <v>1.686022757045232</v>
+        <v>1.717304219798767</v>
       </c>
     </row>
     <row r="323">
@@ -10439,7 +10439,7 @@
         <v>2020</v>
       </c>
       <c r="G323" t="n">
-        <v>15.01660995692176</v>
+        <v>15.14602580868029</v>
       </c>
     </row>
     <row r="324">
@@ -10470,7 +10470,7 @@
         <v>2020</v>
       </c>
       <c r="G324" t="n">
-        <v>14.58541608572048</v>
+        <v>13.87277481024849</v>
       </c>
     </row>
     <row r="325">
@@ -10501,7 +10501,7 @@
         <v>2020</v>
       </c>
       <c r="G325" t="n">
-        <v>11.45196089368085</v>
+        <v>11.40998778315736</v>
       </c>
     </row>
     <row r="326">
@@ -10532,7 +10532,7 @@
         <v>2020</v>
       </c>
       <c r="G326" t="n">
-        <v>7.80604074416134</v>
+        <v>7.262785674825831</v>
       </c>
     </row>
     <row r="327">
@@ -10563,7 +10563,7 @@
         <v>2020</v>
       </c>
       <c r="G327" t="n">
-        <v>3.943539305456452</v>
+        <v>3.509614455021046</v>
       </c>
     </row>
     <row r="328">
@@ -10594,7 +10594,7 @@
         <v>2020</v>
       </c>
       <c r="G328" t="n">
-        <v>16.42723572768724</v>
+        <v>15.68571776209998</v>
       </c>
     </row>
     <row r="329">
@@ -10625,7 +10625,7 @@
         <v>2020</v>
       </c>
       <c r="G329" t="n">
-        <v>4.344997199608932</v>
+        <v>4.115011879719924</v>
       </c>
     </row>
     <row r="330">
@@ -10656,7 +10656,7 @@
         <v>2020</v>
       </c>
       <c r="G330" t="n">
-        <v>9.312105847415765</v>
+        <v>10.73510001447265</v>
       </c>
     </row>
     <row r="331">
@@ -10687,7 +10687,7 @@
         <v>2020</v>
       </c>
       <c r="G331" t="n">
-        <v>12.82857120952355</v>
+        <v>13.31144787351886</v>
       </c>
     </row>
     <row r="332">
@@ -10718,7 +10718,7 @@
         <v>2020</v>
       </c>
       <c r="G332" t="n">
-        <v>15.32755004124069</v>
+        <v>15.63601233240557</v>
       </c>
     </row>
     <row r="333">
@@ -10749,7 +10749,7 @@
         <v>2020</v>
       </c>
       <c r="G333" t="n">
-        <v>12.05773384331897</v>
+        <v>12.11177740365711</v>
       </c>
     </row>
     <row r="334">
@@ -10780,7 +10780,7 @@
         <v>2020</v>
       </c>
       <c r="G334" t="n">
-        <v>10.18667301367063</v>
+        <v>11.10687787974955</v>
       </c>
     </row>
     <row r="335">
@@ -10811,7 +10811,7 @@
         <v>2020</v>
       </c>
       <c r="G335" t="n">
-        <v>17.21783237874463</v>
+        <v>17.32834888558418</v>
       </c>
     </row>
     <row r="336">
@@ -10842,7 +10842,7 @@
         <v>2020</v>
       </c>
       <c r="G336" t="n">
-        <v>8.7832028953624</v>
+        <v>9.310111841597413</v>
       </c>
     </row>
     <row r="337">
@@ -10873,7 +10873,7 @@
         <v>2020</v>
       </c>
       <c r="G337" t="n">
-        <v>4.070631535478094</v>
+        <v>4.027112406890445</v>
       </c>
     </row>
     <row r="338">
@@ -10904,7 +10904,7 @@
         <v>2020</v>
       </c>
       <c r="G338" t="n">
-        <v>3.676273594643447</v>
+        <v>3.732283107980071</v>
       </c>
     </row>
     <row r="339">
@@ -10935,7 +10935,7 @@
         <v>2020</v>
       </c>
       <c r="G339" t="n">
-        <v>16.8297396332907</v>
+        <v>16.25123198191224</v>
       </c>
     </row>
     <row r="340">
@@ -10966,7 +10966,7 @@
         <v>2020</v>
       </c>
       <c r="G340" t="n">
-        <v>9.211450316570181</v>
+        <v>8.860476413419329</v>
       </c>
     </row>
     <row r="341">
@@ -10997,7 +10997,7 @@
         <v>2020</v>
       </c>
       <c r="G341" t="n">
-        <v>6.875557363065063</v>
+        <v>7.222542579260595</v>
       </c>
     </row>
     <row r="342">
@@ -11028,7 +11028,7 @@
         <v>2020</v>
       </c>
       <c r="G342" t="n">
-        <v>6.82099527627705</v>
+        <v>7.41004101540194</v>
       </c>
     </row>
     <row r="343">
@@ -11059,7 +11059,7 @@
         <v>2021</v>
       </c>
       <c r="G343" t="n">
-        <v>2.073619942047102</v>
+        <v>2.113143726403496</v>
       </c>
     </row>
     <row r="344">
@@ -11090,7 +11090,7 @@
         <v>2021</v>
       </c>
       <c r="G344" t="n">
-        <v>9.753259091148994</v>
+        <v>10.82202987280308</v>
       </c>
     </row>
     <row r="345">
@@ -11121,7 +11121,7 @@
         <v>2021</v>
       </c>
       <c r="G345" t="n">
-        <v>8.360340690706057</v>
+        <v>7.490135207359646</v>
       </c>
     </row>
     <row r="346">
@@ -11152,7 +11152,7 @@
         <v>2021</v>
       </c>
       <c r="G346" t="n">
-        <v>6.740765385547463</v>
+        <v>7.574170599567073</v>
       </c>
     </row>
     <row r="347">
@@ -11183,7 +11183,7 @@
         <v>2021</v>
       </c>
       <c r="G347" t="n">
-        <v>2.611601550918531</v>
+        <v>1.981627085454508</v>
       </c>
     </row>
     <row r="348">
@@ -11214,7 +11214,7 @@
         <v>2021</v>
       </c>
       <c r="G348" t="n">
-        <v>5.705007744472393</v>
+        <v>5.649379659938566</v>
       </c>
     </row>
     <row r="349">
@@ -11245,7 +11245,7 @@
         <v>2021</v>
       </c>
       <c r="G349" t="n">
-        <v>3.201577710641155</v>
+        <v>3.163026602886875</v>
       </c>
     </row>
     <row r="350">
@@ -11276,7 +11276,7 @@
         <v>2021</v>
       </c>
       <c r="G350" t="n">
-        <v>1.627575735180494</v>
+        <v>1.215726849456803</v>
       </c>
     </row>
     <row r="351">
@@ -11307,7 +11307,7 @@
         <v>2021</v>
       </c>
       <c r="G351" t="n">
-        <v>14.6505716817068</v>
+        <v>15.23504255022063</v>
       </c>
     </row>
     <row r="352">
@@ -11338,7 +11338,7 @@
         <v>2021</v>
       </c>
       <c r="G352" t="n">
-        <v>4.084175975029431</v>
+        <v>4.183874196183092</v>
       </c>
     </row>
     <row r="353">
@@ -11369,7 +11369,7 @@
         <v>2021</v>
       </c>
       <c r="G353" t="n">
-        <v>1.186452103737517</v>
+        <v>1.562033532680399</v>
       </c>
     </row>
     <row r="354">
@@ -11400,7 +11400,7 @@
         <v>2021</v>
       </c>
       <c r="G354" t="n">
-        <v>24.47235004559079</v>
+        <v>24.73836452660063</v>
       </c>
     </row>
     <row r="355">
@@ -11431,7 +11431,7 @@
         <v>2021</v>
       </c>
       <c r="G355" t="n">
-        <v>10.73591230971</v>
+        <v>11.63886327132367</v>
       </c>
     </row>
     <row r="356">
@@ -11462,7 +11462,7 @@
         <v>2021</v>
       </c>
       <c r="G356" t="n">
-        <v>14.93536193052367</v>
+        <v>14.02940498843768</v>
       </c>
     </row>
     <row r="357">
@@ -11493,7 +11493,7 @@
         <v>2021</v>
       </c>
       <c r="G357" t="n">
-        <v>7.799240595412477</v>
+        <v>7.937741917005589</v>
       </c>
     </row>
     <row r="358">
@@ -11524,7 +11524,7 @@
         <v>2021</v>
       </c>
       <c r="G358" t="n">
-        <v>3.063440142287257</v>
+        <v>3.466288131694262</v>
       </c>
     </row>
     <row r="359">
@@ -11555,7 +11555,7 @@
         <v>2021</v>
       </c>
       <c r="G359" t="n">
-        <v>9.246536975667578</v>
+        <v>8.433046991604899</v>
       </c>
     </row>
     <row r="360">
@@ -11586,7 +11586,7 @@
         <v>2021</v>
       </c>
       <c r="G360" t="n">
-        <v>4.035104030657412</v>
+        <v>3.82287906410811</v>
       </c>
     </row>
     <row r="361">
@@ -11617,7 +11617,7 @@
         <v>2021</v>
       </c>
       <c r="G361" t="n">
-        <v>8.133619515945604</v>
+        <v>8.306290144319329</v>
       </c>
     </row>
     <row r="362">
@@ -11648,7 +11648,7 @@
         <v>2021</v>
       </c>
       <c r="G362" t="n">
-        <v>15.35828082358152</v>
+        <v>14.20406646948719</v>
       </c>
     </row>
     <row r="363">
@@ -11679,7 +11679,7 @@
         <v>2021</v>
       </c>
       <c r="G363" t="n">
-        <v>13.92823822384343</v>
+        <v>14.38373493271603</v>
       </c>
     </row>
     <row r="364">
@@ -11710,7 +11710,7 @@
         <v>2021</v>
       </c>
       <c r="G364" t="n">
-        <v>15.6624208766818</v>
+        <v>15.98382367716773</v>
       </c>
     </row>
     <row r="365">
@@ -11741,7 +11741,7 @@
         <v>2021</v>
       </c>
       <c r="G365" t="n">
-        <v>8.984555761221657</v>
+        <v>9.241883630872646</v>
       </c>
     </row>
     <row r="366">
@@ -11772,7 +11772,7 @@
         <v>2021</v>
       </c>
       <c r="G366" t="n">
-        <v>13.81717801884011</v>
+        <v>14.75656455142232</v>
       </c>
     </row>
     <row r="367">
@@ -11803,7 +11803,7 @@
         <v>2021</v>
       </c>
       <c r="G367" t="n">
-        <v>8.805051668444641</v>
+        <v>9.141335789196878</v>
       </c>
     </row>
     <row r="368">
@@ -11834,7 +11834,7 @@
         <v>2021</v>
       </c>
       <c r="G368" t="n">
-        <v>4.799834016905907</v>
+        <v>4.814340496253664</v>
       </c>
     </row>
     <row r="369">
@@ -11865,7 +11865,7 @@
         <v>2021</v>
       </c>
       <c r="G369" t="n">
-        <v>3.383374318755815</v>
+        <v>3.861699122690416</v>
       </c>
     </row>
     <row r="370">
@@ -11896,7 +11896,7 @@
         <v>2021</v>
       </c>
       <c r="G370" t="n">
-        <v>16.09583251271022</v>
+        <v>16.02228144264672</v>
       </c>
     </row>
     <row r="371">
@@ -11927,7 +11927,7 @@
         <v>2021</v>
       </c>
       <c r="G371" t="n">
-        <v>10.01478177433158</v>
+        <v>10.01244780996343</v>
       </c>
     </row>
     <row r="372">
@@ -11958,7 +11958,7 @@
         <v>2021</v>
       </c>
       <c r="G372" t="n">
-        <v>7.023372957729676</v>
+        <v>7.481592836007287</v>
       </c>
     </row>
     <row r="373">
@@ -11989,7 +11989,7 @@
         <v>2021</v>
       </c>
       <c r="G373" t="n">
-        <v>5.474048965889717</v>
+        <v>5.660272707544835</v>
       </c>
     </row>
     <row r="374">
@@ -12020,7 +12020,7 @@
         <v>2022</v>
       </c>
       <c r="G374" t="n">
-        <v>1.639022781709253</v>
+        <v>1.632069600940893</v>
       </c>
     </row>
     <row r="375">
@@ -12051,7 +12051,7 @@
         <v>2022</v>
       </c>
       <c r="G375" t="n">
-        <v>8.277955086874842</v>
+        <v>8.783381015533761</v>
       </c>
     </row>
     <row r="376">
@@ -12082,7 +12082,7 @@
         <v>2022</v>
       </c>
       <c r="G376" t="n">
-        <v>5.917805586683229</v>
+        <v>5.961183144885917</v>
       </c>
     </row>
     <row r="377">
@@ -12113,7 +12113,7 @@
         <v>2022</v>
       </c>
       <c r="G377" t="n">
-        <v>5.53304710867523</v>
+        <v>5.989257213251258</v>
       </c>
     </row>
     <row r="378">
@@ -12144,7 +12144,7 @@
         <v>2022</v>
       </c>
       <c r="G378" t="n">
-        <v>5.686482011727781</v>
+        <v>5.899102121070797</v>
       </c>
     </row>
     <row r="379">
@@ -12175,7 +12175,7 @@
         <v>2022</v>
       </c>
       <c r="G379" t="n">
-        <v>8.609750593325218</v>
+        <v>8.598342840072602</v>
       </c>
     </row>
     <row r="380">
@@ -12206,7 +12206,7 @@
         <v>2022</v>
       </c>
       <c r="G380" t="n">
-        <v>3.611553016419409</v>
+        <v>3.513582636754464</v>
       </c>
     </row>
     <row r="381">
@@ -12237,7 +12237,7 @@
         <v>2022</v>
       </c>
       <c r="G381" t="n">
-        <v>2.514878170463661</v>
+        <v>2.498838533736135</v>
       </c>
     </row>
     <row r="382">
@@ -12268,7 +12268,7 @@
         <v>2022</v>
       </c>
       <c r="G382" t="n">
-        <v>17.65237903403213</v>
+        <v>18.58498640439519</v>
       </c>
     </row>
     <row r="383">
@@ -12299,7 +12299,7 @@
         <v>2022</v>
       </c>
       <c r="G383" t="n">
-        <v>7.44537224346388</v>
+        <v>8.011626829464879</v>
       </c>
     </row>
     <row r="384">
@@ -12330,7 +12330,7 @@
         <v>2022</v>
       </c>
       <c r="G384" t="n">
-        <v>1.424999858251058</v>
+        <v>1.777576338830109</v>
       </c>
     </row>
     <row r="385">
@@ -12361,7 +12361,7 @@
         <v>2022</v>
       </c>
       <c r="G385" t="n">
-        <v>14.89313118245764</v>
+        <v>14.08864827278695</v>
       </c>
     </row>
     <row r="386">
@@ -12392,7 +12392,7 @@
         <v>2022</v>
       </c>
       <c r="G386" t="n">
-        <v>10.93620490768437</v>
+        <v>11.24135829835569</v>
       </c>
     </row>
     <row r="387">
@@ -12423,7 +12423,7 @@
         <v>2022</v>
       </c>
       <c r="G387" t="n">
-        <v>14.32843736397511</v>
+        <v>15.05218792549612</v>
       </c>
     </row>
     <row r="388">
@@ -12454,7 +12454,7 @@
         <v>2022</v>
       </c>
       <c r="G388" t="n">
-        <v>7.87969246715975</v>
+        <v>7.667922903524947</v>
       </c>
     </row>
     <row r="389">
@@ -12485,7 +12485,7 @@
         <v>2022</v>
       </c>
       <c r="G389" t="n">
-        <v>3.137218072442256</v>
+        <v>3.266828530957659</v>
       </c>
     </row>
     <row r="390">
@@ -12516,7 +12516,7 @@
         <v>2022</v>
       </c>
       <c r="G390" t="n">
-        <v>7.995519682395832</v>
+        <v>6.848301962094064</v>
       </c>
     </row>
     <row r="391">
@@ -12547,7 +12547,7 @@
         <v>2022</v>
       </c>
       <c r="G391" t="n">
-        <v>3.330363827583431</v>
+        <v>3.265879891756664</v>
       </c>
     </row>
     <row r="392">
@@ -12578,7 +12578,7 @@
         <v>2022</v>
       </c>
       <c r="G392" t="n">
-        <v>10.70809480441392</v>
+        <v>10.16925457807965</v>
       </c>
     </row>
     <row r="393">
@@ -12609,7 +12609,7 @@
         <v>2022</v>
       </c>
       <c r="G393" t="n">
-        <v>18.13974162595431</v>
+        <v>18.8166681483101</v>
       </c>
     </row>
     <row r="394">
@@ -12640,7 +12640,7 @@
         <v>2022</v>
       </c>
       <c r="G394" t="n">
-        <v>8.166274044259318</v>
+        <v>8.73379122939895</v>
       </c>
     </row>
     <row r="395">
@@ -12671,7 +12671,7 @@
         <v>2022</v>
       </c>
       <c r="G395" t="n">
-        <v>15.43224756975263</v>
+        <v>13.89993685458227</v>
       </c>
     </row>
     <row r="396">
@@ -12702,7 +12702,7 @@
         <v>2022</v>
       </c>
       <c r="G396" t="n">
-        <v>9.27270991901559</v>
+        <v>9.788437986126137</v>
       </c>
     </row>
     <row r="397">
@@ -12733,7 +12733,7 @@
         <v>2022</v>
       </c>
       <c r="G397" t="n">
-        <v>17.71114979376322</v>
+        <v>19.01399193863356</v>
       </c>
     </row>
     <row r="398">
@@ -12764,7 +12764,7 @@
         <v>2022</v>
       </c>
       <c r="G398" t="n">
-        <v>5.543339023125311</v>
+        <v>5.781167314657571</v>
       </c>
     </row>
     <row r="399">
@@ -12795,7 +12795,7 @@
         <v>2022</v>
       </c>
       <c r="G399" t="n">
-        <v>2.743324110985931</v>
+        <v>3.303653725627219</v>
       </c>
     </row>
     <row r="400">
@@ -12826,7 +12826,7 @@
         <v>2022</v>
       </c>
       <c r="G400" t="n">
-        <v>4.999476007935424</v>
+        <v>5.170760297388713</v>
       </c>
     </row>
     <row r="401">
@@ -12857,7 +12857,7 @@
         <v>2022</v>
       </c>
       <c r="G401" t="n">
-        <v>13.53927713222398</v>
+        <v>12.97272496688859</v>
       </c>
     </row>
     <row r="402">
@@ -12888,7 +12888,7 @@
         <v>2022</v>
       </c>
       <c r="G402" t="n">
-        <v>9.364890060718732</v>
+        <v>9.283956597649865</v>
       </c>
     </row>
     <row r="403">
@@ -12919,7 +12919,7 @@
         <v>2022</v>
       </c>
       <c r="G403" t="n">
-        <v>9.469019349127866</v>
+        <v>9.431995351558733</v>
       </c>
     </row>
     <row r="404">
@@ -12950,7 +12950,7 @@
         <v>2022</v>
       </c>
       <c r="G404" t="n">
-        <v>5.661829858791204</v>
+        <v>6.249444987983808</v>
       </c>
     </row>
     <row r="405">
@@ -12981,7 +12981,7 @@
         <v>2023</v>
       </c>
       <c r="G405" t="n">
-        <v>1.109832004824316</v>
+        <v>1.261743186888937</v>
       </c>
     </row>
     <row r="406">
@@ -13012,7 +13012,7 @@
         <v>2023</v>
       </c>
       <c r="G406" t="n">
-        <v>6.759639869178244</v>
+        <v>6.361651406489788</v>
       </c>
     </row>
     <row r="407">
@@ -13043,7 +13043,7 @@
         <v>2023</v>
       </c>
       <c r="G407" t="n">
-        <v>3.836048253394322</v>
+        <v>4.478614584145308</v>
       </c>
     </row>
     <row r="408">
@@ -13074,7 +13074,7 @@
         <v>2023</v>
       </c>
       <c r="G408" t="n">
-        <v>6.062359722862009</v>
+        <v>6.628284114423814</v>
       </c>
     </row>
     <row r="409">
@@ -13105,7 +13105,7 @@
         <v>2023</v>
       </c>
       <c r="G409" t="n">
-        <v>3.148757539400493</v>
+        <v>2.856841698629068</v>
       </c>
     </row>
     <row r="410">
@@ -13136,7 +13136,7 @@
         <v>2023</v>
       </c>
       <c r="G410" t="n">
-        <v>12.46219799636323</v>
+        <v>12.79279295505636</v>
       </c>
     </row>
     <row r="411">
@@ -13167,7 +13167,7 @@
         <v>2023</v>
       </c>
       <c r="G411" t="n">
-        <v>6.151036939719204</v>
+        <v>5.848966879723712</v>
       </c>
     </row>
     <row r="412">
@@ -13198,7 +13198,7 @@
         <v>2023</v>
       </c>
       <c r="G412" t="n">
-        <v>4.756560143685797</v>
+        <v>4.587284822186003</v>
       </c>
     </row>
     <row r="413">
@@ -13229,7 +13229,7 @@
         <v>2023</v>
       </c>
       <c r="G413" t="n">
-        <v>20.69805036824046</v>
+        <v>21.07083366762069</v>
       </c>
     </row>
     <row r="414">
@@ -13260,7 +13260,7 @@
         <v>2023</v>
       </c>
       <c r="G414" t="n">
-        <v>5.478204655472515</v>
+        <v>5.820645502831047</v>
       </c>
     </row>
     <row r="415">
@@ -13291,7 +13291,7 @@
         <v>2023</v>
       </c>
       <c r="G415" t="n">
-        <v>2.213759428879279</v>
+        <v>2.15471022417047</v>
       </c>
     </row>
     <row r="416">
@@ -13322,7 +13322,7 @@
         <v>2023</v>
       </c>
       <c r="G416" t="n">
-        <v>17.34149918777257</v>
+        <v>17.03253647968549</v>
       </c>
     </row>
     <row r="417">
@@ -13353,7 +13353,7 @@
         <v>2023</v>
       </c>
       <c r="G417" t="n">
-        <v>7.240965446802843</v>
+        <v>6.527894088995525</v>
       </c>
     </row>
     <row r="418">
@@ -13384,7 +13384,7 @@
         <v>2023</v>
       </c>
       <c r="G418" t="n">
-        <v>17.2353749904977</v>
+        <v>16.1978412992272</v>
       </c>
     </row>
     <row r="419">
@@ -13415,7 +13415,7 @@
         <v>2023</v>
       </c>
       <c r="G419" t="n">
-        <v>9.210005500009839</v>
+        <v>9.169188813981226</v>
       </c>
     </row>
     <row r="420">
@@ -13446,7 +13446,7 @@
         <v>2023</v>
       </c>
       <c r="G420" t="n">
-        <v>2.366128542163502</v>
+        <v>2.390720978970417</v>
       </c>
     </row>
     <row r="421">
@@ -13477,7 +13477,7 @@
         <v>2023</v>
       </c>
       <c r="G421" t="n">
-        <v>6.955726395791244</v>
+        <v>6.758905087390519</v>
       </c>
     </row>
     <row r="422">
@@ -13508,7 +13508,7 @@
         <v>2023</v>
       </c>
       <c r="G422" t="n">
-        <v>1.98176856022757</v>
+        <v>1.549008959904554</v>
       </c>
     </row>
     <row r="423">
@@ -13539,7 +13539,7 @@
         <v>2023</v>
       </c>
       <c r="G423" t="n">
-        <v>10.80927441339733</v>
+        <v>11.00710811480013</v>
       </c>
     </row>
     <row r="424">
@@ -13570,7 +13570,7 @@
         <v>2023</v>
       </c>
       <c r="G424" t="n">
-        <v>16.29323619171154</v>
+        <v>16.3351436255261</v>
       </c>
     </row>
     <row r="425">
@@ -13601,7 +13601,7 @@
         <v>2023</v>
       </c>
       <c r="G425" t="n">
-        <v>8.56781403320192</v>
+        <v>8.771829657478831</v>
       </c>
     </row>
     <row r="426">
@@ -13632,7 +13632,7 @@
         <v>2023</v>
       </c>
       <c r="G426" t="n">
-        <v>13.33056659496676</v>
+        <v>12.11688307035842</v>
       </c>
     </row>
     <row r="427">
@@ -13663,7 +13663,7 @@
         <v>2023</v>
       </c>
       <c r="G427" t="n">
-        <v>9.278146809815793</v>
+        <v>9.832529237576342</v>
       </c>
     </row>
     <row r="428">
@@ -13694,7 +13694,7 @@
         <v>2023</v>
       </c>
       <c r="G428" t="n">
-        <v>32.85608184698777</v>
+        <v>30.50723687635899</v>
       </c>
     </row>
     <row r="429">
@@ -13725,7 +13725,7 @@
         <v>2023</v>
       </c>
       <c r="G429" t="n">
-        <v>4.338281918700967</v>
+        <v>5.180166805084379</v>
       </c>
     </row>
     <row r="430">
@@ -13756,7 +13756,7 @@
         <v>2023</v>
       </c>
       <c r="G430" t="n">
-        <v>4.72390014646044</v>
+        <v>5.471041247315275</v>
       </c>
     </row>
     <row r="431">
@@ -13787,7 +13787,7 @@
         <v>2023</v>
       </c>
       <c r="G431" t="n">
-        <v>4.48164420476235</v>
+        <v>4.023803077848864</v>
       </c>
     </row>
     <row r="432">
@@ -13818,7 +13818,7 @@
         <v>2023</v>
       </c>
       <c r="G432" t="n">
-        <v>12.095628813054</v>
+        <v>11.60333160113212</v>
       </c>
     </row>
     <row r="433">
@@ -13849,7 +13849,7 @@
         <v>2023</v>
       </c>
       <c r="G433" t="n">
-        <v>9.161674161045088</v>
+        <v>9.419800987075613</v>
       </c>
     </row>
     <row r="434">
@@ -13880,7 +13880,7 @@
         <v>2023</v>
       </c>
       <c r="G434" t="n">
-        <v>8.486380431048651</v>
+        <v>8.657815079110083</v>
       </c>
     </row>
     <row r="435">
@@ -13911,7 +13911,7 @@
         <v>2023</v>
       </c>
       <c r="G435" t="n">
-        <v>4.717623057805247</v>
+        <v>4.707011878536052</v>
       </c>
     </row>
     <row r="436">
@@ -13942,7 +13942,7 @@
         <v>2024</v>
       </c>
       <c r="G436" t="n">
-        <v>0.1764646566501966</v>
+        <v>0.3956754102529254</v>
       </c>
     </row>
     <row r="437">
@@ -13973,7 +13973,7 @@
         <v>2024</v>
       </c>
       <c r="G437" t="n">
-        <v>5.359905703831608</v>
+        <v>5.413762232872797</v>
       </c>
     </row>
     <row r="438">
@@ -14004,7 +14004,7 @@
         <v>2024</v>
       </c>
       <c r="G438" t="n">
-        <v>3.550841471240072</v>
+        <v>3.881660186897745</v>
       </c>
     </row>
     <row r="439">
@@ -14035,7 +14035,7 @@
         <v>2024</v>
       </c>
       <c r="G439" t="n">
-        <v>3.71231389518669</v>
+        <v>4.942974531309342</v>
       </c>
     </row>
     <row r="440">
@@ -14066,7 +14066,7 @@
         <v>2024</v>
       </c>
       <c r="G440" t="n">
-        <v>2.624890888696819</v>
+        <v>2.370101250999963</v>
       </c>
     </row>
     <row r="441">
@@ -14097,7 +14097,7 @@
         <v>2024</v>
       </c>
       <c r="G441" t="n">
-        <v>10.77651917343015</v>
+        <v>10.81691881915634</v>
       </c>
     </row>
     <row r="442">
@@ -14128,7 +14128,7 @@
         <v>2024</v>
       </c>
       <c r="G442" t="n">
-        <v>6.080354443679038</v>
+        <v>5.824136068311685</v>
       </c>
     </row>
     <row r="443">
@@ -14159,7 +14159,7 @@
         <v>2024</v>
       </c>
       <c r="G443" t="n">
-        <v>3.602466702692393</v>
+        <v>3.072888521567755</v>
       </c>
     </row>
     <row r="444">
@@ -14190,7 +14190,7 @@
         <v>2024</v>
       </c>
       <c r="G444" t="n">
-        <v>21.52386210704303</v>
+        <v>21.84041317275728</v>
       </c>
     </row>
     <row r="445">
@@ -14221,7 +14221,7 @@
         <v>2024</v>
       </c>
       <c r="G445" t="n">
-        <v>4.870629275831217</v>
+        <v>5.159826842956684</v>
       </c>
     </row>
     <row r="446">
@@ -14252,7 +14252,7 @@
         <v>2024</v>
       </c>
       <c r="G446" t="n">
-        <v>2.275708200933</v>
+        <v>2.506479165258153</v>
       </c>
     </row>
     <row r="447">
@@ -14283,7 +14283,7 @@
         <v>2024</v>
       </c>
       <c r="G447" t="n">
-        <v>12.62468382166389</v>
+        <v>11.99440297073092</v>
       </c>
     </row>
     <row r="448">
@@ -14314,7 +14314,7 @@
         <v>2024</v>
       </c>
       <c r="G448" t="n">
-        <v>18.76512809765809</v>
+        <v>19.1991058486579</v>
       </c>
     </row>
     <row r="449">
@@ -14345,7 +14345,7 @@
         <v>2024</v>
       </c>
       <c r="G449" t="n">
-        <v>14.45350523250413</v>
+        <v>15.2532241191985</v>
       </c>
     </row>
     <row r="450">
@@ -14376,7 +14376,7 @@
         <v>2024</v>
       </c>
       <c r="G450" t="n">
-        <v>7.636562588882217</v>
+        <v>7.740456025029233</v>
       </c>
     </row>
     <row r="451">
@@ -14407,7 +14407,7 @@
         <v>2024</v>
       </c>
       <c r="G451" t="n">
-        <v>2.209577648988287</v>
+        <v>1.897916457925739</v>
       </c>
     </row>
     <row r="452">
@@ -14438,7 +14438,7 @@
         <v>2024</v>
       </c>
       <c r="G452" t="n">
-        <v>2.130110379704801</v>
+        <v>2.190644533074132</v>
       </c>
     </row>
     <row r="453">
@@ -14469,7 +14469,7 @@
         <v>2024</v>
       </c>
       <c r="G453" t="n">
-        <v>0.5680278211475842</v>
+        <v>0.6401765161723781</v>
       </c>
     </row>
     <row r="454">
@@ -14500,7 +14500,7 @@
         <v>2024</v>
       </c>
       <c r="G454" t="n">
-        <v>8.397816806666034</v>
+        <v>7.221638253077585</v>
       </c>
     </row>
     <row r="455">
@@ -14531,7 +14531,7 @@
         <v>2024</v>
       </c>
       <c r="G455" t="n">
-        <v>15.88604770650031</v>
+        <v>16.67709664859791</v>
       </c>
     </row>
     <row r="456">
@@ -14562,7 +14562,7 @@
         <v>2024</v>
       </c>
       <c r="G456" t="n">
-        <v>7.328100086829585</v>
+        <v>7.584980110171911</v>
       </c>
     </row>
     <row r="457">
@@ -14593,7 +14593,7 @@
         <v>2024</v>
       </c>
       <c r="G457" t="n">
-        <v>11.19636045815872</v>
+        <v>11.5967188117014</v>
       </c>
     </row>
     <row r="458">
@@ -14624,7 +14624,7 @@
         <v>2024</v>
       </c>
       <c r="G458" t="n">
-        <v>9.18991008686228</v>
+        <v>9.591606363798812</v>
       </c>
     </row>
     <row r="459">
@@ -14655,7 +14655,7 @@
         <v>2024</v>
       </c>
       <c r="G459" t="n">
-        <v>21.65457021298536</v>
+        <v>21.56194786816691</v>
       </c>
     </row>
     <row r="460">
@@ -14686,7 +14686,7 @@
         <v>2024</v>
       </c>
       <c r="G460" t="n">
-        <v>8.423505332742794</v>
+        <v>9.393164956025849</v>
       </c>
     </row>
     <row r="461">
@@ -14717,7 +14717,7 @@
         <v>2024</v>
       </c>
       <c r="G461" t="n">
-        <v>7.655293577424055</v>
+        <v>8.386398963967544</v>
       </c>
     </row>
     <row r="462">
@@ -14748,7 +14748,7 @@
         <v>2024</v>
       </c>
       <c r="G462" t="n">
-        <v>1.733279339559779</v>
+        <v>1.964766092438264</v>
       </c>
     </row>
     <row r="463">
@@ -14779,7 +14779,7 @@
         <v>2024</v>
       </c>
       <c r="G463" t="n">
-        <v>11.78167319852587</v>
+        <v>11.44583927677233</v>
       </c>
     </row>
     <row r="464">
@@ -14810,7 +14810,7 @@
         <v>2024</v>
       </c>
       <c r="G464" t="n">
-        <v>9.427191613688874</v>
+        <v>9.843682716661032</v>
       </c>
     </row>
     <row r="465">
@@ -14841,7 +14841,7 @@
         <v>2024</v>
       </c>
       <c r="G465" t="n">
-        <v>8.124244292754364</v>
+        <v>7.775896371160044</v>
       </c>
     </row>
     <row r="466">
@@ -14872,7 +14872,7 @@
         <v>2024</v>
       </c>
       <c r="G466" t="n">
-        <v>5.188661263884123</v>
+        <v>5.317883520350244</v>
       </c>
     </row>
   </sheetData>
